--- a/data.xlsx
+++ b/data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Deepanshi Ahuja\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Deepanshi Ahuja\Desktop\used_cars_dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD175452-DC19-413F-9529-16766A34FBEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55FA245F-E30C-4E3E-905B-B8390CA38ABC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{D7CE9FC5-F49F-40D4-93B4-AA39BB343A99}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="data" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">data!$A$1:$F$773</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">data!$A$1:$F$896</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2691" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2790" uniqueCount="18">
   <si>
     <t>Date</t>
   </si>
@@ -468,7 +468,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22A7DA2E-DF85-4559-9E8B-F6EDBCD02D26}">
-  <dimension ref="A1:F896"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:F929"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.08984375" bestFit="1" customWidth="1"/>
@@ -496,7 +497,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>46115</v>
       </c>
@@ -516,7 +517,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>46117</v>
       </c>
@@ -536,7 +537,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>46118</v>
       </c>
@@ -556,7 +557,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>46119</v>
       </c>
@@ -576,7 +577,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>46119</v>
       </c>
@@ -596,7 +597,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>46119</v>
       </c>
@@ -616,7 +617,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>46120</v>
       </c>
@@ -636,7 +637,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>46120</v>
       </c>
@@ -656,7 +657,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>46120</v>
       </c>
@@ -676,7 +677,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>46120</v>
       </c>
@@ -696,7 +697,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>46120</v>
       </c>
@@ -716,7 +717,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <v>46120</v>
       </c>
@@ -736,7 +737,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <v>46120</v>
       </c>
@@ -756,7 +757,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <v>46121</v>
       </c>
@@ -776,7 +777,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <v>46121</v>
       </c>
@@ -796,7 +797,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <v>46121</v>
       </c>
@@ -816,7 +817,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
         <v>46121</v>
       </c>
@@ -836,7 +837,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
         <v>46121</v>
       </c>
@@ -856,7 +857,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
         <v>46121</v>
       </c>
@@ -876,7 +877,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
         <v>46121</v>
       </c>
@@ -896,7 +897,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
         <v>46122</v>
       </c>
@@ -916,7 +917,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
         <v>46122</v>
       </c>
@@ -936,7 +937,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
         <v>46122</v>
       </c>
@@ -956,7 +957,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
         <v>46122</v>
       </c>
@@ -976,7 +977,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
         <v>46122</v>
       </c>
@@ -996,7 +997,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
         <v>46122</v>
       </c>
@@ -1016,7 +1017,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
         <v>46122</v>
       </c>
@@ -1036,7 +1037,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A29" s="1">
         <v>46122</v>
       </c>
@@ -1056,7 +1057,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A30" s="1">
         <v>46123</v>
       </c>
@@ -1076,7 +1077,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A31" s="1">
         <v>46123</v>
       </c>
@@ -1096,7 +1097,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A32" s="1">
         <v>46123</v>
       </c>
@@ -1116,7 +1117,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A33" s="1">
         <v>46123</v>
       </c>
@@ -1136,7 +1137,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A34" s="1">
         <v>46123</v>
       </c>
@@ -1156,7 +1157,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A35" s="1">
         <v>46123</v>
       </c>
@@ -1176,7 +1177,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A36" s="1">
         <v>46123</v>
       </c>
@@ -1196,7 +1197,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A37" s="1">
         <v>46123</v>
       </c>
@@ -1216,7 +1217,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A38" s="1">
         <v>46124</v>
       </c>
@@ -1236,7 +1237,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A39" s="1">
         <v>46124</v>
       </c>
@@ -1256,7 +1257,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A40" s="1">
         <v>46124</v>
       </c>
@@ -1276,7 +1277,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A41" s="1">
         <v>46124</v>
       </c>
@@ -1296,7 +1297,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A42" s="1">
         <v>46124</v>
       </c>
@@ -1316,7 +1317,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A43" s="1">
         <v>46124</v>
       </c>
@@ -1336,7 +1337,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A44" s="1">
         <v>46124</v>
       </c>
@@ -1356,7 +1357,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A45" s="1">
         <v>46124</v>
       </c>
@@ -1376,7 +1377,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A46" s="1">
         <v>46124</v>
       </c>
@@ -1396,7 +1397,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A47" s="1">
         <v>46125</v>
       </c>
@@ -1416,7 +1417,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A48" s="1">
         <v>46125</v>
       </c>
@@ -1436,7 +1437,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A49" s="1">
         <v>46125</v>
       </c>
@@ -1456,7 +1457,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A50" s="1">
         <v>46125</v>
       </c>
@@ -1476,7 +1477,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A51" s="1">
         <v>46125</v>
       </c>
@@ -1496,7 +1497,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A52" s="1">
         <v>46125</v>
       </c>
@@ -1516,7 +1517,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A53" s="1">
         <v>46125</v>
       </c>
@@ -1536,7 +1537,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A54" s="1">
         <v>46125</v>
       </c>
@@ -1556,7 +1557,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A55" s="1">
         <v>46125</v>
       </c>
@@ -1576,7 +1577,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A56" s="1">
         <v>46126</v>
       </c>
@@ -1596,7 +1597,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A57" s="1">
         <v>46126</v>
       </c>
@@ -1616,7 +1617,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A58" s="1">
         <v>46126</v>
       </c>
@@ -1636,7 +1637,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A59" s="1">
         <v>46126</v>
       </c>
@@ -1656,7 +1657,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A60" s="1">
         <v>46126</v>
       </c>
@@ -1676,7 +1677,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A61" s="1">
         <v>46126</v>
       </c>
@@ -1696,7 +1697,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A62" s="1">
         <v>46126</v>
       </c>
@@ -1716,7 +1717,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A63" s="1">
         <v>46126</v>
       </c>
@@ -1736,7 +1737,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A64" s="1">
         <v>46126</v>
       </c>
@@ -1756,7 +1757,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A65" s="1">
         <v>46126</v>
       </c>
@@ -1776,7 +1777,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A66" s="1">
         <v>46127</v>
       </c>
@@ -1796,7 +1797,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A67" s="1">
         <v>46127</v>
       </c>
@@ -1816,7 +1817,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A68" s="1">
         <v>46127</v>
       </c>
@@ -1836,7 +1837,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A69" s="1">
         <v>46127</v>
       </c>
@@ -1856,7 +1857,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A70" s="1">
         <v>46127</v>
       </c>
@@ -1876,7 +1877,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A71" s="1">
         <v>46127</v>
       </c>
@@ -1896,7 +1897,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A72" s="1">
         <v>46127</v>
       </c>
@@ -1916,7 +1917,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A73" s="1">
         <v>46127</v>
       </c>
@@ -1936,7 +1937,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A74" s="1">
         <v>46127</v>
       </c>
@@ -1956,7 +1957,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A75" s="1">
         <v>46128</v>
       </c>
@@ -1976,7 +1977,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A76" s="1">
         <v>46128</v>
       </c>
@@ -1996,7 +1997,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A77" s="1">
         <v>46128</v>
       </c>
@@ -2016,7 +2017,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A78" s="1">
         <v>46128</v>
       </c>
@@ -2036,7 +2037,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A79" s="1">
         <v>46128</v>
       </c>
@@ -2056,7 +2057,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A80" s="1">
         <v>46128</v>
       </c>
@@ -2076,7 +2077,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A81" s="1">
         <v>46128</v>
       </c>
@@ -2096,7 +2097,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A82" s="1">
         <v>46128</v>
       </c>
@@ -2116,7 +2117,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A83" s="1">
         <v>46128</v>
       </c>
@@ -2136,7 +2137,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A84" s="1">
         <v>46129</v>
       </c>
@@ -2156,7 +2157,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A85" s="1">
         <v>46129</v>
       </c>
@@ -2176,7 +2177,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A86" s="1">
         <v>46129</v>
       </c>
@@ -2196,7 +2197,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A87" s="1">
         <v>46129</v>
       </c>
@@ -2216,7 +2217,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A88" s="1">
         <v>46129</v>
       </c>
@@ -2236,7 +2237,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A89" s="1">
         <v>46129</v>
       </c>
@@ -2256,7 +2257,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A90" s="1">
         <v>46129</v>
       </c>
@@ -2276,7 +2277,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A91" s="1">
         <v>46129</v>
       </c>
@@ -2296,7 +2297,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A92" s="1">
         <v>46130</v>
       </c>
@@ -2316,7 +2317,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A93" s="1">
         <v>46130</v>
       </c>
@@ -2336,7 +2337,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A94" s="1">
         <v>46130</v>
       </c>
@@ -2356,7 +2357,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A95" s="1">
         <v>46130</v>
       </c>
@@ -2376,7 +2377,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A96" s="1">
         <v>46130</v>
       </c>
@@ -2396,7 +2397,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A97" s="1">
         <v>46130</v>
       </c>
@@ -2416,7 +2417,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A98" s="1">
         <v>46130</v>
       </c>
@@ -2436,7 +2437,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A99" s="1">
         <v>46130</v>
       </c>
@@ -2456,7 +2457,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A100" s="1">
         <v>46130</v>
       </c>
@@ -2476,7 +2477,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A101" s="1">
         <v>46131</v>
       </c>
@@ -2496,7 +2497,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A102" s="1">
         <v>46131</v>
       </c>
@@ -2516,7 +2517,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A103" s="1">
         <v>46131</v>
       </c>
@@ -2536,7 +2537,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A104" s="1">
         <v>46131</v>
       </c>
@@ -2556,7 +2557,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A105" s="1">
         <v>46131</v>
       </c>
@@ -2576,7 +2577,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A106" s="1">
         <v>46131</v>
       </c>
@@ -2596,7 +2597,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A107" s="1">
         <v>46131</v>
       </c>
@@ -2616,7 +2617,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A108" s="1">
         <v>46131</v>
       </c>
@@ -2636,7 +2637,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A109" s="1">
         <v>46132</v>
       </c>
@@ -2656,7 +2657,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A110" s="1">
         <v>46132</v>
       </c>
@@ -2676,7 +2677,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A111" s="1">
         <v>46132</v>
       </c>
@@ -2696,7 +2697,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A112" s="1">
         <v>46132</v>
       </c>
@@ -2716,7 +2717,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A113" s="1">
         <v>46132</v>
       </c>
@@ -2736,7 +2737,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A114" s="1">
         <v>46132</v>
       </c>
@@ -2756,7 +2757,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A115" s="1">
         <v>46132</v>
       </c>
@@ -2776,7 +2777,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A116" s="1">
         <v>46132</v>
       </c>
@@ -2796,7 +2797,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A117" s="1">
         <v>46132</v>
       </c>
@@ -2816,7 +2817,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A118" s="1">
         <v>46132</v>
       </c>
@@ -2836,7 +2837,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A119" s="1">
         <v>46132</v>
       </c>
@@ -2856,7 +2857,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A120" s="1">
         <v>46132</v>
       </c>
@@ -2876,7 +2877,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A121" s="1">
         <v>46133</v>
       </c>
@@ -2896,7 +2897,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A122" s="1">
         <v>46133</v>
       </c>
@@ -2916,7 +2917,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A123" s="1">
         <v>46133</v>
       </c>
@@ -2936,7 +2937,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A124" s="1">
         <v>46133</v>
       </c>
@@ -2956,7 +2957,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A125" s="1">
         <v>46133</v>
       </c>
@@ -2976,7 +2977,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A126" s="1">
         <v>46133</v>
       </c>
@@ -2996,7 +2997,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A127" s="1">
         <v>46133</v>
       </c>
@@ -3016,7 +3017,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A128" s="1">
         <v>46133</v>
       </c>
@@ -3036,7 +3037,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A129" s="1">
         <v>46133</v>
       </c>
@@ -3056,7 +3057,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A130" s="1">
         <v>46133</v>
       </c>
@@ -3076,7 +3077,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A131" s="1">
         <v>46133</v>
       </c>
@@ -3096,7 +3097,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A132" s="1">
         <v>46133</v>
       </c>
@@ -3116,7 +3117,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A133" s="1">
         <v>46134</v>
       </c>
@@ -3136,7 +3137,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A134" s="1">
         <v>46134</v>
       </c>
@@ -3156,7 +3157,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A135" s="1">
         <v>46134</v>
       </c>
@@ -3176,7 +3177,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A136" s="1">
         <v>46134</v>
       </c>
@@ -3196,7 +3197,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A137" s="1">
         <v>46134</v>
       </c>
@@ -3216,7 +3217,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A138" s="1">
         <v>46134</v>
       </c>
@@ -3236,7 +3237,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A139" s="1">
         <v>46134</v>
       </c>
@@ -3256,7 +3257,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A140" s="1">
         <v>46134</v>
       </c>
@@ -3276,7 +3277,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A141" s="1">
         <v>46134</v>
       </c>
@@ -3296,7 +3297,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A142" s="1">
         <v>46134</v>
       </c>
@@ -3316,7 +3317,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A143" s="1">
         <v>46134</v>
       </c>
@@ -3336,7 +3337,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A144" s="1">
         <v>46134</v>
       </c>
@@ -3356,7 +3357,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A145" s="1">
         <v>46134</v>
       </c>
@@ -3376,7 +3377,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A146" s="1">
         <v>46134</v>
       </c>
@@ -3396,7 +3397,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A147" s="1">
         <v>46135</v>
       </c>
@@ -3416,7 +3417,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A148" s="1">
         <v>46135</v>
       </c>
@@ -3436,7 +3437,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A149" s="1">
         <v>46135</v>
       </c>
@@ -3456,7 +3457,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A150" s="1">
         <v>46135</v>
       </c>
@@ -3476,7 +3477,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A151" s="1">
         <v>46135</v>
       </c>
@@ -3496,7 +3497,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A152" s="1">
         <v>46135</v>
       </c>
@@ -3516,7 +3517,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A153" s="1">
         <v>46135</v>
       </c>
@@ -3536,7 +3537,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A154" s="1">
         <v>46135</v>
       </c>
@@ -3556,7 +3557,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A155" s="1">
         <v>46135</v>
       </c>
@@ -3576,7 +3577,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A156" s="1">
         <v>46135</v>
       </c>
@@ -3596,7 +3597,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A157" s="1">
         <v>46135</v>
       </c>
@@ -3616,7 +3617,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A158" s="1">
         <v>46135</v>
       </c>
@@ -3636,7 +3637,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A159" s="1">
         <v>46135</v>
       </c>
@@ -3656,7 +3657,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A160" s="1">
         <v>46136</v>
       </c>
@@ -3676,7 +3677,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A161" s="1">
         <v>46136</v>
       </c>
@@ -3696,7 +3697,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A162" s="1">
         <v>46136</v>
       </c>
@@ -3716,7 +3717,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A163" s="1">
         <v>46136</v>
       </c>
@@ -3736,7 +3737,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A164" s="1">
         <v>46136</v>
       </c>
@@ -3756,7 +3757,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A165" s="1">
         <v>46136</v>
       </c>
@@ -3776,7 +3777,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A166" s="1">
         <v>46136</v>
       </c>
@@ -3796,7 +3797,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A167" s="1">
         <v>46136</v>
       </c>
@@ -3816,7 +3817,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A168" s="1">
         <v>46136</v>
       </c>
@@ -3836,7 +3837,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A169" s="1">
         <v>46136</v>
       </c>
@@ -3856,7 +3857,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A170" s="1">
         <v>46136</v>
       </c>
@@ -3876,7 +3877,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A171" s="1">
         <v>46136</v>
       </c>
@@ -3896,7 +3897,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A172" s="1">
         <v>46137</v>
       </c>
@@ -3916,7 +3917,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A173" s="1">
         <v>46137</v>
       </c>
@@ -3936,7 +3937,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A174" s="1">
         <v>46137</v>
       </c>
@@ -3956,7 +3957,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A175" s="1">
         <v>46137</v>
       </c>
@@ -3976,7 +3977,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A176" s="1">
         <v>46137</v>
       </c>
@@ -3996,7 +3997,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A177" s="1">
         <v>46137</v>
       </c>
@@ -4016,7 +4017,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A178" s="1">
         <v>46137</v>
       </c>
@@ -4036,7 +4037,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A179" s="1">
         <v>46137</v>
       </c>
@@ -4056,7 +4057,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A180" s="1">
         <v>46137</v>
       </c>
@@ -4076,7 +4077,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A181" s="1">
         <v>46137</v>
       </c>
@@ -4096,7 +4097,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A182" s="1">
         <v>46137</v>
       </c>
@@ -4116,7 +4117,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A183" s="1">
         <v>46137</v>
       </c>
@@ -4136,7 +4137,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A184" s="1">
         <v>46137</v>
       </c>
@@ -4156,7 +4157,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A185" s="1">
         <v>46137</v>
       </c>
@@ -4176,7 +4177,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A186" s="1">
         <v>46137</v>
       </c>
@@ -4196,7 +4197,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A187" s="1">
         <v>46137</v>
       </c>
@@ -4216,7 +4217,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A188" s="1">
         <v>46138</v>
       </c>
@@ -4236,7 +4237,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A189" s="1">
         <v>46138</v>
       </c>
@@ -4256,7 +4257,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A190" s="1">
         <v>46138</v>
       </c>
@@ -4276,7 +4277,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A191" s="1">
         <v>46138</v>
       </c>
@@ -4296,7 +4297,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A192" s="1">
         <v>46138</v>
       </c>
@@ -4316,7 +4317,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="193" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A193" s="1">
         <v>46138</v>
       </c>
@@ -4336,7 +4337,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="194" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A194" s="1">
         <v>46138</v>
       </c>
@@ -4356,7 +4357,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="195" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A195" s="1">
         <v>46138</v>
       </c>
@@ -4376,7 +4377,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="196" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A196" s="1">
         <v>46138</v>
       </c>
@@ -4396,7 +4397,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="197" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A197" s="1">
         <v>46138</v>
       </c>
@@ -4416,7 +4417,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="198" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A198" s="1">
         <v>46138</v>
       </c>
@@ -4436,7 +4437,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="199" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A199" s="1">
         <v>46138</v>
       </c>
@@ -4456,7 +4457,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="200" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A200" s="1">
         <v>46138</v>
       </c>
@@ -4476,7 +4477,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="201" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A201" s="1">
         <v>46138</v>
       </c>
@@ -4496,7 +4497,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="202" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A202" s="1">
         <v>46138</v>
       </c>
@@ -4516,7 +4517,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="203" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A203" s="1">
         <v>46138</v>
       </c>
@@ -4536,7 +4537,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="204" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A204" s="1">
         <v>46139</v>
       </c>
@@ -4556,7 +4557,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="205" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A205" s="1">
         <v>46139</v>
       </c>
@@ -4576,7 +4577,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="206" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A206" s="1">
         <v>46139</v>
       </c>
@@ -4596,7 +4597,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="207" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A207" s="1">
         <v>46139</v>
       </c>
@@ -4616,7 +4617,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="208" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A208" s="1">
         <v>46139</v>
       </c>
@@ -4636,7 +4637,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="209" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A209" s="1">
         <v>46139</v>
       </c>
@@ -4656,7 +4657,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="210" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A210" s="1">
         <v>46139</v>
       </c>
@@ -4676,7 +4677,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="211" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A211" s="1">
         <v>46139</v>
       </c>
@@ -4696,7 +4697,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="212" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A212" s="1">
         <v>46139</v>
       </c>
@@ -4716,7 +4717,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="213" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A213" s="1">
         <v>46139</v>
       </c>
@@ -4736,7 +4737,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="214" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A214" s="1">
         <v>46139</v>
       </c>
@@ -4756,7 +4757,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="215" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A215" s="1">
         <v>46139</v>
       </c>
@@ -4776,7 +4777,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="216" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A216" s="1">
         <v>46139</v>
       </c>
@@ -4796,7 +4797,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="217" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A217" s="1">
         <v>46139</v>
       </c>
@@ -4816,7 +4817,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="218" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A218" s="1">
         <v>46139</v>
       </c>
@@ -4836,7 +4837,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="219" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A219" s="1">
         <v>46139</v>
       </c>
@@ -4856,7 +4857,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="220" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A220" s="1">
         <v>46139</v>
       </c>
@@ -4876,7 +4877,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="221" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A221" s="1">
         <v>46140</v>
       </c>
@@ -4896,7 +4897,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="222" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A222" s="1">
         <v>46140</v>
       </c>
@@ -4916,7 +4917,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="223" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A223" s="1">
         <v>46140</v>
       </c>
@@ -4936,7 +4937,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="224" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A224" s="1">
         <v>46140</v>
       </c>
@@ -4956,7 +4957,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="225" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A225" s="1">
         <v>46140</v>
       </c>
@@ -4976,7 +4977,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="226" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A226" s="1">
         <v>46140</v>
       </c>
@@ -4996,7 +4997,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="227" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A227" s="1">
         <v>46140</v>
       </c>
@@ -5016,7 +5017,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="228" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A228" s="1">
         <v>46140</v>
       </c>
@@ -5036,7 +5037,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="229" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A229" s="1">
         <v>46140</v>
       </c>
@@ -5056,7 +5057,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="230" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A230" s="1">
         <v>46140</v>
       </c>
@@ -5076,7 +5077,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="231" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A231" s="1">
         <v>46140</v>
       </c>
@@ -5096,7 +5097,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="232" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A232" s="1">
         <v>46140</v>
       </c>
@@ -5116,7 +5117,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="233" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A233" s="1">
         <v>46140</v>
       </c>
@@ -5136,7 +5137,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="234" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A234" s="1">
         <v>46140</v>
       </c>
@@ -5156,7 +5157,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="235" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A235" s="1">
         <v>46140</v>
       </c>
@@ -5176,7 +5177,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="236" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A236" s="1">
         <v>46140</v>
       </c>
@@ -5196,7 +5197,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="237" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A237" s="1">
         <v>46140</v>
       </c>
@@ -5216,7 +5217,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="238" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A238" s="1">
         <v>46141</v>
       </c>
@@ -5236,7 +5237,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="239" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A239" s="1">
         <v>46141</v>
       </c>
@@ -5256,7 +5257,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="240" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A240" s="1">
         <v>46141</v>
       </c>
@@ -5276,7 +5277,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="241" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A241" s="1">
         <v>46141</v>
       </c>
@@ -5296,7 +5297,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="242" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A242" s="1">
         <v>46141</v>
       </c>
@@ -5316,7 +5317,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="243" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A243" s="1">
         <v>46141</v>
       </c>
@@ -5336,7 +5337,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="244" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A244" s="1">
         <v>46141</v>
       </c>
@@ -5356,7 +5357,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="245" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A245" s="1">
         <v>46141</v>
       </c>
@@ -5376,7 +5377,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="246" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A246" s="1">
         <v>46141</v>
       </c>
@@ -5396,7 +5397,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="247" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A247" s="1">
         <v>46141</v>
       </c>
@@ -5416,7 +5417,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="248" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A248" s="1">
         <v>46141</v>
       </c>
@@ -5436,7 +5437,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="249" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A249" s="1">
         <v>46141</v>
       </c>
@@ -5456,7 +5457,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="250" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A250" s="1">
         <v>46141</v>
       </c>
@@ -5476,7 +5477,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="251" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A251" s="1">
         <v>46141</v>
       </c>
@@ -5496,7 +5497,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="252" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A252" s="1">
         <v>46141</v>
       </c>
@@ -5516,7 +5517,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="253" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A253" s="1">
         <v>46141</v>
       </c>
@@ -5536,7 +5537,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="254" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A254" s="1">
         <v>46142</v>
       </c>
@@ -5556,7 +5557,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="255" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A255" s="1">
         <v>46142</v>
       </c>
@@ -5576,7 +5577,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="256" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A256" s="1">
         <v>46142</v>
       </c>
@@ -5596,7 +5597,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="257" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A257" s="1">
         <v>46142</v>
       </c>
@@ -5616,7 +5617,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="258" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A258" s="1">
         <v>46142</v>
       </c>
@@ -5636,7 +5637,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="259" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A259" s="1">
         <v>46142</v>
       </c>
@@ -5656,7 +5657,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="260" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A260" s="1">
         <v>46142</v>
       </c>
@@ -5676,7 +5677,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="261" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A261" s="1">
         <v>46142</v>
       </c>
@@ -5696,7 +5697,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="262" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A262" s="1">
         <v>46142</v>
       </c>
@@ -5716,7 +5717,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="263" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A263" s="1">
         <v>46142</v>
       </c>
@@ -5736,7 +5737,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="264" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A264" s="1">
         <v>46142</v>
       </c>
@@ -5756,7 +5757,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="265" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A265" s="1">
         <v>46142</v>
       </c>
@@ -5776,7 +5777,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="266" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A266" s="1">
         <v>46142</v>
       </c>
@@ -5796,7 +5797,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="267" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A267" s="1">
         <v>46142</v>
       </c>
@@ -5816,7 +5817,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="268" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A268" s="1">
         <v>46142</v>
       </c>
@@ -5836,7 +5837,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="269" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A269" s="1">
         <v>46142</v>
       </c>
@@ -5856,7 +5857,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="270" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A270" s="1">
         <v>46143</v>
       </c>
@@ -5876,7 +5877,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="271" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A271" s="1">
         <v>46143</v>
       </c>
@@ -5896,7 +5897,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="272" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A272" s="1">
         <v>46143</v>
       </c>
@@ -5916,7 +5917,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="273" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A273" s="1">
         <v>46143</v>
       </c>
@@ -5936,7 +5937,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="274" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A274" s="1">
         <v>46143</v>
       </c>
@@ -5956,7 +5957,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="275" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A275" s="1">
         <v>46143</v>
       </c>
@@ -5976,7 +5977,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="276" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A276" s="1">
         <v>46143</v>
       </c>
@@ -5996,7 +5997,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="277" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A277" s="1">
         <v>46143</v>
       </c>
@@ -6016,7 +6017,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="278" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A278" s="1">
         <v>46143</v>
       </c>
@@ -6036,7 +6037,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="279" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A279" s="1">
         <v>46143</v>
       </c>
@@ -6056,7 +6057,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="280" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A280" s="1">
         <v>46143</v>
       </c>
@@ -6076,7 +6077,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="281" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A281" s="1">
         <v>46143</v>
       </c>
@@ -6096,7 +6097,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="282" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A282" s="1">
         <v>46143</v>
       </c>
@@ -6116,7 +6117,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="283" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A283" s="1">
         <v>46143</v>
       </c>
@@ -6136,7 +6137,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="284" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A284" s="1">
         <v>46143</v>
       </c>
@@ -6156,7 +6157,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="285" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A285" s="1">
         <v>46143</v>
       </c>
@@ -6176,7 +6177,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="286" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A286" s="1">
         <v>46144</v>
       </c>
@@ -6196,7 +6197,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="287" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A287" s="1">
         <v>46144</v>
       </c>
@@ -6216,7 +6217,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="288" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A288" s="1">
         <v>46144</v>
       </c>
@@ -6236,7 +6237,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="289" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A289" s="1">
         <v>46144</v>
       </c>
@@ -6256,7 +6257,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="290" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A290" s="1">
         <v>46144</v>
       </c>
@@ -6276,7 +6277,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="291" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A291" s="1">
         <v>46144</v>
       </c>
@@ -6296,7 +6297,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="292" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A292" s="1">
         <v>46144</v>
       </c>
@@ -6316,7 +6317,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="293" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A293" s="1">
         <v>46144</v>
       </c>
@@ -6336,7 +6337,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="294" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A294" s="1">
         <v>46144</v>
       </c>
@@ -6356,7 +6357,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="295" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A295" s="1">
         <v>46144</v>
       </c>
@@ -6376,7 +6377,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="296" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A296" s="1">
         <v>46144</v>
       </c>
@@ -6396,7 +6397,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="297" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A297" s="1">
         <v>46144</v>
       </c>
@@ -6416,7 +6417,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="298" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A298" s="1">
         <v>46144</v>
       </c>
@@ -6436,7 +6437,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="299" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A299" s="1">
         <v>46144</v>
       </c>
@@ -6456,7 +6457,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="300" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A300" s="1">
         <v>46144</v>
       </c>
@@ -6476,7 +6477,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="301" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A301" s="1">
         <v>46144</v>
       </c>
@@ -6496,7 +6497,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="302" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A302" s="1">
         <v>46144</v>
       </c>
@@ -6516,7 +6517,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="303" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A303" s="1">
         <v>46145</v>
       </c>
@@ -6536,7 +6537,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="304" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A304" s="1">
         <v>46145</v>
       </c>
@@ -6556,7 +6557,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="305" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A305" s="1">
         <v>46145</v>
       </c>
@@ -6576,7 +6577,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="306" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A306" s="1">
         <v>46145</v>
       </c>
@@ -6596,7 +6597,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="307" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A307" s="1">
         <v>46145</v>
       </c>
@@ -6616,7 +6617,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="308" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A308" s="1">
         <v>46145</v>
       </c>
@@ -6636,7 +6637,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="309" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A309" s="1">
         <v>46145</v>
       </c>
@@ -6656,7 +6657,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="310" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A310" s="1">
         <v>46145</v>
       </c>
@@ -6676,7 +6677,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="311" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A311" s="1">
         <v>46145</v>
       </c>
@@ -6696,7 +6697,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="312" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A312" s="1">
         <v>46145</v>
       </c>
@@ -6716,7 +6717,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="313" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A313" s="1">
         <v>46145</v>
       </c>
@@ -6736,7 +6737,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="314" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A314" s="1">
         <v>46145</v>
       </c>
@@ -6756,7 +6757,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="315" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A315" s="1">
         <v>46145</v>
       </c>
@@ -6776,7 +6777,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="316" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A316" s="1">
         <v>46145</v>
       </c>
@@ -6796,7 +6797,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="317" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A317" s="1">
         <v>46146</v>
       </c>
@@ -6816,7 +6817,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="318" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A318" s="1">
         <v>46146</v>
       </c>
@@ -6836,7 +6837,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="319" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A319" s="1">
         <v>46146</v>
       </c>
@@ -6856,7 +6857,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="320" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A320" s="1">
         <v>46146</v>
       </c>
@@ -6876,7 +6877,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="321" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A321" s="1">
         <v>46146</v>
       </c>
@@ -6896,7 +6897,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="322" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A322" s="1">
         <v>46146</v>
       </c>
@@ -6916,7 +6917,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="323" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A323" s="1">
         <v>46146</v>
       </c>
@@ -6936,7 +6937,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="324" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A324" s="1">
         <v>46146</v>
       </c>
@@ -6956,7 +6957,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="325" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A325" s="1">
         <v>46146</v>
       </c>
@@ -6976,7 +6977,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="326" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A326" s="1">
         <v>46146</v>
       </c>
@@ -6996,7 +6997,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="327" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A327" s="1">
         <v>46146</v>
       </c>
@@ -7016,7 +7017,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="328" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A328" s="1">
         <v>46146</v>
       </c>
@@ -7036,7 +7037,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="329" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A329" s="1">
         <v>46146</v>
       </c>
@@ -7056,7 +7057,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="330" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A330" s="1">
         <v>46146</v>
       </c>
@@ -7076,7 +7077,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="331" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A331" s="1">
         <v>46146</v>
       </c>
@@ -7096,7 +7097,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="332" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A332" s="1">
         <v>46146</v>
       </c>
@@ -7116,7 +7117,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="333" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A333" s="1">
         <v>46147</v>
       </c>
@@ -7136,7 +7137,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="334" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A334" s="1">
         <v>46147</v>
       </c>
@@ -7156,7 +7157,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="335" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A335" s="1">
         <v>46147</v>
       </c>
@@ -7176,7 +7177,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="336" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A336" s="1">
         <v>46147</v>
       </c>
@@ -7196,7 +7197,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="337" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A337" s="1">
         <v>46147</v>
       </c>
@@ -7216,7 +7217,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="338" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A338" s="1">
         <v>46147</v>
       </c>
@@ -7236,7 +7237,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="339" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A339" s="1">
         <v>46147</v>
       </c>
@@ -7256,7 +7257,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="340" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A340" s="1">
         <v>46147</v>
       </c>
@@ -7276,7 +7277,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="341" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A341" s="1">
         <v>46147</v>
       </c>
@@ -7296,7 +7297,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="342" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A342" s="1">
         <v>46147</v>
       </c>
@@ -7316,7 +7317,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="343" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A343" s="1">
         <v>46147</v>
       </c>
@@ -7336,7 +7337,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="344" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A344" s="1">
         <v>46147</v>
       </c>
@@ -7356,7 +7357,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="345" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A345" s="1">
         <v>46147</v>
       </c>
@@ -7376,7 +7377,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="346" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A346" s="1">
         <v>46147</v>
       </c>
@@ -7396,7 +7397,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="347" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A347" s="1">
         <v>46147</v>
       </c>
@@ -7416,7 +7417,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="348" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A348" s="1">
         <v>46147</v>
       </c>
@@ -7436,7 +7437,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="349" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A349" s="1">
         <v>46147</v>
       </c>
@@ -7456,7 +7457,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="350" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A350" s="1">
         <v>46148</v>
       </c>
@@ -7476,7 +7477,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="351" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A351" s="1">
         <v>46148</v>
       </c>
@@ -7496,7 +7497,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="352" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A352" s="1">
         <v>46148</v>
       </c>
@@ -7516,7 +7517,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="353" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A353" s="1">
         <v>46148</v>
       </c>
@@ -7536,7 +7537,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="354" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A354" s="1">
         <v>46148</v>
       </c>
@@ -7556,7 +7557,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="355" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A355" s="1">
         <v>46148</v>
       </c>
@@ -7576,7 +7577,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="356" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A356" s="1">
         <v>46148</v>
       </c>
@@ -7596,7 +7597,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="357" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A357" s="1">
         <v>46148</v>
       </c>
@@ -7616,7 +7617,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="358" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A358" s="1">
         <v>46148</v>
       </c>
@@ -7636,7 +7637,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="359" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A359" s="1">
         <v>46148</v>
       </c>
@@ -7656,7 +7657,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="360" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A360" s="1">
         <v>46148</v>
       </c>
@@ -7676,7 +7677,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="361" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A361" s="1">
         <v>46148</v>
       </c>
@@ -7696,7 +7697,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="362" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A362" s="1">
         <v>46148</v>
       </c>
@@ -7716,7 +7717,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="363" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A363" s="1">
         <v>46148</v>
       </c>
@@ -7736,7 +7737,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="364" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A364" s="1">
         <v>46148</v>
       </c>
@@ -7756,7 +7757,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="365" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A365" s="1">
         <v>46149</v>
       </c>
@@ -7776,7 +7777,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="366" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A366" s="1">
         <v>46149</v>
       </c>
@@ -7796,7 +7797,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="367" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A367" s="1">
         <v>46149</v>
       </c>
@@ -7816,7 +7817,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="368" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A368" s="1">
         <v>46149</v>
       </c>
@@ -7836,7 +7837,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="369" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A369" s="1">
         <v>46149</v>
       </c>
@@ -7856,7 +7857,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="370" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A370" s="1">
         <v>46149</v>
       </c>
@@ -7876,7 +7877,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="371" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A371" s="1">
         <v>46149</v>
       </c>
@@ -7896,7 +7897,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="372" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A372" s="1">
         <v>46149</v>
       </c>
@@ -7916,7 +7917,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="373" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A373" s="1">
         <v>46149</v>
       </c>
@@ -7936,7 +7937,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="374" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A374" s="1">
         <v>46149</v>
       </c>
@@ -7956,7 +7957,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="375" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A375" s="1">
         <v>46149</v>
       </c>
@@ -7976,7 +7977,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="376" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A376" s="1">
         <v>46149</v>
       </c>
@@ -7996,7 +7997,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="377" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A377" s="1">
         <v>46149</v>
       </c>
@@ -8016,7 +8017,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="378" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A378" s="1">
         <v>46149</v>
       </c>
@@ -8036,7 +8037,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="379" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A379" s="1">
         <v>46149</v>
       </c>
@@ -8056,7 +8057,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="380" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A380" s="1">
         <v>46149</v>
       </c>
@@ -8076,7 +8077,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="381" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A381" s="1">
         <v>46150</v>
       </c>
@@ -8096,7 +8097,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="382" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A382" s="1">
         <v>46150</v>
       </c>
@@ -8116,7 +8117,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="383" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="383" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A383" s="1">
         <v>46150</v>
       </c>
@@ -8136,7 +8137,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="384" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A384" s="1">
         <v>46150</v>
       </c>
@@ -8156,7 +8157,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="385" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A385" s="1">
         <v>46150</v>
       </c>
@@ -8176,7 +8177,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="386" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="386" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A386" s="1">
         <v>46150</v>
       </c>
@@ -8196,7 +8197,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="387" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="387" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A387" s="1">
         <v>46150</v>
       </c>
@@ -8216,7 +8217,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="388" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="388" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A388" s="1">
         <v>46150</v>
       </c>
@@ -8236,7 +8237,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="389" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="389" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A389" s="1">
         <v>46150</v>
       </c>
@@ -8256,7 +8257,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="390" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="390" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A390" s="1">
         <v>46150</v>
       </c>
@@ -8276,7 +8277,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="391" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="391" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A391" s="1">
         <v>46150</v>
       </c>
@@ -8296,7 +8297,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="392" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="392" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A392" s="1">
         <v>46150</v>
       </c>
@@ -8316,7 +8317,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="393" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="393" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A393" s="1">
         <v>46150</v>
       </c>
@@ -8336,7 +8337,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="394" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="394" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A394" s="1">
         <v>46150</v>
       </c>
@@ -8356,7 +8357,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="395" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="395" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A395" s="1">
         <v>46150</v>
       </c>
@@ -8376,7 +8377,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="396" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="396" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A396" s="1">
         <v>46150</v>
       </c>
@@ -8396,7 +8397,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="397" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="397" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A397" s="1">
         <v>46151</v>
       </c>
@@ -8416,7 +8417,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="398" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="398" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A398" s="1">
         <v>46151</v>
       </c>
@@ -8436,7 +8437,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="399" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="399" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A399" s="1">
         <v>46151</v>
       </c>
@@ -8456,7 +8457,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="400" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="400" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A400" s="1">
         <v>46151</v>
       </c>
@@ -8476,7 +8477,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="401" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="401" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A401" s="1">
         <v>46151</v>
       </c>
@@ -8496,7 +8497,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="402" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="402" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A402" s="1">
         <v>46151</v>
       </c>
@@ -8516,7 +8517,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="403" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="403" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A403" s="1">
         <v>46151</v>
       </c>
@@ -8536,7 +8537,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="404" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="404" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A404" s="1">
         <v>46151</v>
       </c>
@@ -8556,7 +8557,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="405" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="405" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A405" s="1">
         <v>46151</v>
       </c>
@@ -8576,7 +8577,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="406" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="406" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A406" s="1">
         <v>46151</v>
       </c>
@@ -8596,7 +8597,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="407" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="407" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A407" s="1">
         <v>46151</v>
       </c>
@@ -8616,7 +8617,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="408" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="408" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A408" s="1">
         <v>46151</v>
       </c>
@@ -8636,7 +8637,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="409" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="409" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A409" s="1">
         <v>46151</v>
       </c>
@@ -8656,7 +8657,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="410" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="410" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A410" s="1">
         <v>46151</v>
       </c>
@@ -8676,7 +8677,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="411" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="411" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A411" s="1">
         <v>46151</v>
       </c>
@@ -8696,7 +8697,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="412" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="412" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A412" s="1">
         <v>46151</v>
       </c>
@@ -8716,7 +8717,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="413" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="413" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A413" s="1">
         <v>46152</v>
       </c>
@@ -8736,7 +8737,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="414" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="414" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A414" s="1">
         <v>46152</v>
       </c>
@@ -8756,7 +8757,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="415" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="415" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A415" s="1">
         <v>46152</v>
       </c>
@@ -8776,7 +8777,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="416" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="416" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A416" s="1">
         <v>46152</v>
       </c>
@@ -8796,7 +8797,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="417" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="417" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A417" s="1">
         <v>46152</v>
       </c>
@@ -8816,7 +8817,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="418" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="418" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A418" s="1">
         <v>46152</v>
       </c>
@@ -8836,7 +8837,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="419" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="419" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A419" s="1">
         <v>46152</v>
       </c>
@@ -8856,7 +8857,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="420" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="420" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A420" s="1">
         <v>46152</v>
       </c>
@@ -8876,7 +8877,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="421" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="421" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A421" s="1">
         <v>46152</v>
       </c>
@@ -8896,7 +8897,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="422" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="422" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A422" s="1">
         <v>46152</v>
       </c>
@@ -8916,7 +8917,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="423" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="423" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A423" s="1">
         <v>46152</v>
       </c>
@@ -8936,7 +8937,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="424" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="424" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A424" s="1">
         <v>46152</v>
       </c>
@@ -8956,7 +8957,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="425" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="425" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A425" s="1">
         <v>46152</v>
       </c>
@@ -8976,7 +8977,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="426" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="426" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A426" s="1">
         <v>46152</v>
       </c>
@@ -8996,7 +8997,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="427" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="427" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A427" s="1">
         <v>46152</v>
       </c>
@@ -9016,7 +9017,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="428" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="428" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A428" s="1">
         <v>46153</v>
       </c>
@@ -9036,7 +9037,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="429" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="429" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A429" s="1">
         <v>46153</v>
       </c>
@@ -9056,7 +9057,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="430" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="430" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A430" s="1">
         <v>46153</v>
       </c>
@@ -9076,7 +9077,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="431" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="431" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A431" s="1">
         <v>46153</v>
       </c>
@@ -9096,7 +9097,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="432" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="432" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A432" s="1">
         <v>46153</v>
       </c>
@@ -9116,7 +9117,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="433" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="433" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A433" s="1">
         <v>46153</v>
       </c>
@@ -9136,7 +9137,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="434" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="434" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A434" s="1">
         <v>46153</v>
       </c>
@@ -9156,7 +9157,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="435" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="435" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A435" s="1">
         <v>46153</v>
       </c>
@@ -9176,7 +9177,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="436" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="436" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A436" s="1">
         <v>46153</v>
       </c>
@@ -9196,7 +9197,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="437" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="437" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A437" s="1">
         <v>46153</v>
       </c>
@@ -9216,7 +9217,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="438" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="438" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A438" s="1">
         <v>46153</v>
       </c>
@@ -9236,7 +9237,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="439" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="439" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A439" s="1">
         <v>46153</v>
       </c>
@@ -9256,7 +9257,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="440" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="440" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A440" s="1">
         <v>46153</v>
       </c>
@@ -9276,7 +9277,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="441" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="441" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A441" s="1">
         <v>46153</v>
       </c>
@@ -9296,7 +9297,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="442" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="442" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A442" s="1">
         <v>46153</v>
       </c>
@@ -9316,7 +9317,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="443" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="443" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A443" s="1">
         <v>46153</v>
       </c>
@@ -9336,7 +9337,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="444" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="444" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A444" s="1">
         <v>46154</v>
       </c>
@@ -9356,7 +9357,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="445" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="445" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A445" s="1">
         <v>46154</v>
       </c>
@@ -9376,7 +9377,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="446" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="446" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A446" s="1">
         <v>46154</v>
       </c>
@@ -9396,7 +9397,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="447" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="447" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A447" s="1">
         <v>46154</v>
       </c>
@@ -9416,7 +9417,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="448" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="448" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A448" s="1">
         <v>46154</v>
       </c>
@@ -9436,7 +9437,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="449" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="449" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A449" s="1">
         <v>46154</v>
       </c>
@@ -9456,7 +9457,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="450" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="450" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A450" s="1">
         <v>46154</v>
       </c>
@@ -9476,7 +9477,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="451" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="451" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A451" s="1">
         <v>46154</v>
       </c>
@@ -9496,7 +9497,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="452" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="452" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A452" s="1">
         <v>46154</v>
       </c>
@@ -9516,7 +9517,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="453" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="453" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A453" s="1">
         <v>46154</v>
       </c>
@@ -9536,7 +9537,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="454" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="454" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A454" s="1">
         <v>46154</v>
       </c>
@@ -9556,7 +9557,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="455" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="455" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A455" s="1">
         <v>46154</v>
       </c>
@@ -9576,7 +9577,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="456" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="456" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A456" s="1">
         <v>46154</v>
       </c>
@@ -9596,7 +9597,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="457" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="457" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A457" s="1">
         <v>46154</v>
       </c>
@@ -9616,7 +9617,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="458" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="458" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A458" s="1">
         <v>46154</v>
       </c>
@@ -9636,7 +9637,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="459" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="459" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A459" s="1">
         <v>46154</v>
       </c>
@@ -9656,7 +9657,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="460" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="460" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A460" s="1">
         <v>46155</v>
       </c>
@@ -9676,7 +9677,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="461" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="461" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A461" s="1">
         <v>46155</v>
       </c>
@@ -9696,7 +9697,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="462" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="462" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A462" s="1">
         <v>46155</v>
       </c>
@@ -9716,7 +9717,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="463" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="463" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A463" s="1">
         <v>46155</v>
       </c>
@@ -9736,7 +9737,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="464" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="464" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A464" s="1">
         <v>46155</v>
       </c>
@@ -9756,7 +9757,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="465" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="465" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A465" s="1">
         <v>46155</v>
       </c>
@@ -9776,7 +9777,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="466" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="466" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A466" s="1">
         <v>46155</v>
       </c>
@@ -9796,7 +9797,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="467" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="467" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A467" s="1">
         <v>46155</v>
       </c>
@@ -9816,7 +9817,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="468" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="468" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A468" s="1">
         <v>46155</v>
       </c>
@@ -9836,7 +9837,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="469" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="469" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A469" s="1">
         <v>46155</v>
       </c>
@@ -9856,7 +9857,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="470" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="470" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A470" s="1">
         <v>46155</v>
       </c>
@@ -9876,7 +9877,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="471" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="471" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A471" s="1">
         <v>46155</v>
       </c>
@@ -9896,7 +9897,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="472" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="472" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A472" s="1">
         <v>46155</v>
       </c>
@@ -9916,7 +9917,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="473" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="473" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A473" s="1">
         <v>46155</v>
       </c>
@@ -9936,7 +9937,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="474" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="474" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A474" s="1">
         <v>46155</v>
       </c>
@@ -9956,7 +9957,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="475" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="475" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A475" s="1">
         <v>46155</v>
       </c>
@@ -9976,7 +9977,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="476" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="476" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A476" s="1">
         <v>46156</v>
       </c>
@@ -9996,7 +9997,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="477" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="477" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A477" s="1">
         <v>46156</v>
       </c>
@@ -10016,7 +10017,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="478" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="478" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A478" s="1">
         <v>46156</v>
       </c>
@@ -10036,7 +10037,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="479" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="479" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A479" s="1">
         <v>46156</v>
       </c>
@@ -10056,7 +10057,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="480" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="480" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A480" s="1">
         <v>46156</v>
       </c>
@@ -10076,7 +10077,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="481" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="481" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A481" s="1">
         <v>46156</v>
       </c>
@@ -10096,7 +10097,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="482" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="482" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A482" s="1">
         <v>46156</v>
       </c>
@@ -10116,7 +10117,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="483" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="483" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A483" s="1">
         <v>46156</v>
       </c>
@@ -10136,7 +10137,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="484" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="484" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A484" s="1">
         <v>46156</v>
       </c>
@@ -10156,7 +10157,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="485" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="485" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A485" s="1">
         <v>46156</v>
       </c>
@@ -10176,7 +10177,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="486" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="486" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A486" s="1">
         <v>46156</v>
       </c>
@@ -10196,7 +10197,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="487" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="487" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A487" s="1">
         <v>46156</v>
       </c>
@@ -10216,7 +10217,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="488" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="488" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A488" s="1">
         <v>46156</v>
       </c>
@@ -10236,7 +10237,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="489" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="489" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A489" s="1">
         <v>46156</v>
       </c>
@@ -10256,7 +10257,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="490" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="490" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A490" s="1">
         <v>46156</v>
       </c>
@@ -10276,7 +10277,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="491" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="491" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A491" s="1">
         <v>46156</v>
       </c>
@@ -10296,7 +10297,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="492" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="492" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A492" s="1">
         <v>46157</v>
       </c>
@@ -10316,7 +10317,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="493" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="493" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A493" s="1">
         <v>46157</v>
       </c>
@@ -10336,7 +10337,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="494" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="494" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A494" s="1">
         <v>46157</v>
       </c>
@@ -10356,7 +10357,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="495" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="495" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A495" s="1">
         <v>46157</v>
       </c>
@@ -10376,7 +10377,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="496" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="496" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A496" s="1">
         <v>46157</v>
       </c>
@@ -10396,7 +10397,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="497" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="497" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A497" s="1">
         <v>46157</v>
       </c>
@@ -10416,7 +10417,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="498" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="498" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A498" s="1">
         <v>46157</v>
       </c>
@@ -10436,7 +10437,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="499" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="499" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A499" s="1">
         <v>46157</v>
       </c>
@@ -10456,7 +10457,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="500" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="500" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A500" s="1">
         <v>46157</v>
       </c>
@@ -10476,7 +10477,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="501" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="501" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A501" s="1">
         <v>46157</v>
       </c>
@@ -10496,7 +10497,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="502" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="502" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A502" s="1">
         <v>46157</v>
       </c>
@@ -10516,7 +10517,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="503" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="503" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A503" s="1">
         <v>46157</v>
       </c>
@@ -10536,7 +10537,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="504" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="504" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A504" s="1">
         <v>46157</v>
       </c>
@@ -10556,7 +10557,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="505" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="505" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A505" s="1">
         <v>46157</v>
       </c>
@@ -10576,7 +10577,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="506" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="506" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A506" s="1">
         <v>46157</v>
       </c>
@@ -10596,7 +10597,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="507" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="507" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A507" s="1">
         <v>46157</v>
       </c>
@@ -10616,7 +10617,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="508" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="508" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A508" s="1">
         <v>46157</v>
       </c>
@@ -10636,7 +10637,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="509" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="509" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A509" s="1">
         <v>46157</v>
       </c>
@@ -10656,7 +10657,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="510" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="510" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A510" s="1">
         <v>46158</v>
       </c>
@@ -10676,7 +10677,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="511" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="511" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A511" s="1">
         <v>46158</v>
       </c>
@@ -10696,7 +10697,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="512" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="512" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A512" s="1">
         <v>46158</v>
       </c>
@@ -10716,7 +10717,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="513" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="513" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A513" s="1">
         <v>46158</v>
       </c>
@@ -10736,7 +10737,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="514" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="514" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A514" s="1">
         <v>46158</v>
       </c>
@@ -10756,7 +10757,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="515" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="515" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A515" s="1">
         <v>46158</v>
       </c>
@@ -10776,7 +10777,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="516" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="516" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A516" s="1">
         <v>46158</v>
       </c>
@@ -10796,7 +10797,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="517" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="517" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A517" s="1">
         <v>46158</v>
       </c>
@@ -10816,7 +10817,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="518" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="518" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A518" s="1">
         <v>46158</v>
       </c>
@@ -10836,7 +10837,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="519" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="519" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A519" s="1">
         <v>46158</v>
       </c>
@@ -10856,7 +10857,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="520" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="520" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A520" s="1">
         <v>46158</v>
       </c>
@@ -10876,7 +10877,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="521" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="521" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A521" s="1">
         <v>46158</v>
       </c>
@@ -10896,7 +10897,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="522" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="522" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A522" s="1">
         <v>46158</v>
       </c>
@@ -10916,7 +10917,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="523" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="523" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A523" s="1">
         <v>46158</v>
       </c>
@@ -10936,7 +10937,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="524" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="524" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A524" s="1">
         <v>46158</v>
       </c>
@@ -10956,7 +10957,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="525" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="525" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A525" s="1">
         <v>46158</v>
       </c>
@@ -10976,7 +10977,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="526" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="526" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A526" s="1">
         <v>46158</v>
       </c>
@@ -10996,7 +10997,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="527" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="527" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A527" s="1">
         <v>46159</v>
       </c>
@@ -11016,7 +11017,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="528" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="528" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A528" s="1">
         <v>46159</v>
       </c>
@@ -11036,7 +11037,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="529" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="529" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A529" s="1">
         <v>46159</v>
       </c>
@@ -11056,7 +11057,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="530" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="530" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A530" s="1">
         <v>46159</v>
       </c>
@@ -11076,7 +11077,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="531" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="531" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A531" s="1">
         <v>46159</v>
       </c>
@@ -11096,7 +11097,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="532" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="532" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A532" s="1">
         <v>46159</v>
       </c>
@@ -11116,7 +11117,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="533" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="533" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A533" s="1">
         <v>46159</v>
       </c>
@@ -11136,7 +11137,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="534" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="534" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A534" s="1">
         <v>46159</v>
       </c>
@@ -11156,7 +11157,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="535" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="535" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A535" s="1">
         <v>46159</v>
       </c>
@@ -11176,7 +11177,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="536" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="536" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A536" s="1">
         <v>46159</v>
       </c>
@@ -11196,7 +11197,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="537" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="537" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A537" s="1">
         <v>46159</v>
       </c>
@@ -11216,7 +11217,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="538" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="538" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A538" s="1">
         <v>46159</v>
       </c>
@@ -11236,7 +11237,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="539" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="539" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A539" s="1">
         <v>46159</v>
       </c>
@@ -11256,7 +11257,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="540" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="540" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A540" s="1">
         <v>46159</v>
       </c>
@@ -11276,7 +11277,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="541" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="541" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A541" s="1">
         <v>46159</v>
       </c>
@@ -11296,7 +11297,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="542" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="542" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A542" s="1">
         <v>46159</v>
       </c>
@@ -11316,7 +11317,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="543" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="543" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A543" s="1">
         <v>46159</v>
       </c>
@@ -11336,7 +11337,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="544" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="544" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A544" s="1">
         <v>46159</v>
       </c>
@@ -11356,7 +11357,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="545" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="545" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A545" s="1">
         <v>46160</v>
       </c>
@@ -11376,7 +11377,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="546" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="546" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A546" s="1">
         <v>46160</v>
       </c>
@@ -11396,7 +11397,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="547" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="547" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A547" s="1">
         <v>46160</v>
       </c>
@@ -11416,7 +11417,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="548" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="548" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A548" s="1">
         <v>46160</v>
       </c>
@@ -11436,7 +11437,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="549" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="549" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A549" s="1">
         <v>46160</v>
       </c>
@@ -11456,7 +11457,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="550" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="550" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A550" s="1">
         <v>46160</v>
       </c>
@@ -11476,7 +11477,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="551" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="551" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A551" s="1">
         <v>46160</v>
       </c>
@@ -11496,7 +11497,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="552" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="552" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A552" s="1">
         <v>46160</v>
       </c>
@@ -11516,7 +11517,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="553" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="553" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A553" s="1">
         <v>46160</v>
       </c>
@@ -11536,7 +11537,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="554" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="554" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A554" s="1">
         <v>46160</v>
       </c>
@@ -11556,7 +11557,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="555" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="555" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A555" s="1">
         <v>46160</v>
       </c>
@@ -11576,7 +11577,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="556" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="556" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A556" s="1">
         <v>46160</v>
       </c>
@@ -11596,7 +11597,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="557" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="557" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A557" s="1">
         <v>46160</v>
       </c>
@@ -11616,7 +11617,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="558" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="558" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A558" s="1">
         <v>46160</v>
       </c>
@@ -11636,7 +11637,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="559" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="559" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A559" s="1">
         <v>46160</v>
       </c>
@@ -11656,7 +11657,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="560" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="560" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A560" s="1">
         <v>46160</v>
       </c>
@@ -11676,7 +11677,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="561" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="561" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A561" s="1">
         <v>46160</v>
       </c>
@@ -11696,7 +11697,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="562" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="562" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A562" s="1">
         <v>46161</v>
       </c>
@@ -11716,7 +11717,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="563" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="563" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A563" s="1">
         <v>46161</v>
       </c>
@@ -11736,7 +11737,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="564" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="564" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A564" s="1">
         <v>46161</v>
       </c>
@@ -11756,7 +11757,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="565" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="565" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A565" s="1">
         <v>46161</v>
       </c>
@@ -11776,7 +11777,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="566" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="566" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A566" s="1">
         <v>46161</v>
       </c>
@@ -11796,7 +11797,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="567" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="567" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A567" s="1">
         <v>46161</v>
       </c>
@@ -11816,7 +11817,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="568" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="568" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A568" s="1">
         <v>46161</v>
       </c>
@@ -11836,7 +11837,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="569" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="569" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A569" s="1">
         <v>46161</v>
       </c>
@@ -11856,7 +11857,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="570" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="570" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A570" s="1">
         <v>46161</v>
       </c>
@@ -11876,7 +11877,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="571" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="571" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A571" s="1">
         <v>46161</v>
       </c>
@@ -11896,7 +11897,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="572" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="572" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A572" s="1">
         <v>46161</v>
       </c>
@@ -11916,7 +11917,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="573" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="573" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A573" s="1">
         <v>46161</v>
       </c>
@@ -11936,7 +11937,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="574" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="574" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A574" s="1">
         <v>46161</v>
       </c>
@@ -11956,7 +11957,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="575" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="575" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A575" s="1">
         <v>46161</v>
       </c>
@@ -11976,7 +11977,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="576" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="576" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A576" s="1">
         <v>46161</v>
       </c>
@@ -11996,7 +11997,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="577" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="577" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A577" s="1">
         <v>46161</v>
       </c>
@@ -12016,7 +12017,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="578" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="578" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A578" s="1">
         <v>46162</v>
       </c>
@@ -12036,7 +12037,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="579" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="579" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A579" s="1">
         <v>46162</v>
       </c>
@@ -12056,7 +12057,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="580" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="580" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A580" s="1">
         <v>46162</v>
       </c>
@@ -12076,7 +12077,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="581" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="581" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A581" s="1">
         <v>46162</v>
       </c>
@@ -12096,7 +12097,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="582" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="582" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A582" s="1">
         <v>46162</v>
       </c>
@@ -12116,7 +12117,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="583" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="583" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A583" s="1">
         <v>46162</v>
       </c>
@@ -12136,7 +12137,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="584" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="584" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A584" s="1">
         <v>46162</v>
       </c>
@@ -12156,7 +12157,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="585" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="585" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A585" s="1">
         <v>46162</v>
       </c>
@@ -12176,7 +12177,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="586" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="586" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A586" s="1">
         <v>46162</v>
       </c>
@@ -12196,7 +12197,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="587" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="587" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A587" s="1">
         <v>46162</v>
       </c>
@@ -12216,7 +12217,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="588" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="588" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A588" s="1">
         <v>46162</v>
       </c>
@@ -12236,7 +12237,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="589" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="589" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A589" s="1">
         <v>46162</v>
       </c>
@@ -12256,7 +12257,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="590" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="590" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A590" s="1">
         <v>46162</v>
       </c>
@@ -12276,7 +12277,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="591" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="591" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A591" s="1">
         <v>46162</v>
       </c>
@@ -12296,7 +12297,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="592" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="592" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A592" s="1">
         <v>46162</v>
       </c>
@@ -12316,7 +12317,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="593" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="593" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A593" s="1">
         <v>46162</v>
       </c>
@@ -12336,7 +12337,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="594" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="594" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A594" s="1">
         <v>46163</v>
       </c>
@@ -12356,7 +12357,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="595" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="595" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A595" s="1">
         <v>46163</v>
       </c>
@@ -12376,7 +12377,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="596" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="596" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A596" s="1">
         <v>46163</v>
       </c>
@@ -12396,7 +12397,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="597" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="597" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A597" s="1">
         <v>46163</v>
       </c>
@@ -12416,7 +12417,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="598" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="598" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A598" s="1">
         <v>46163</v>
       </c>
@@ -12436,7 +12437,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="599" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="599" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A599" s="1">
         <v>46163</v>
       </c>
@@ -12456,7 +12457,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="600" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="600" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A600" s="1">
         <v>46163</v>
       </c>
@@ -12476,7 +12477,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="601" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="601" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A601" s="1">
         <v>46163</v>
       </c>
@@ -12496,7 +12497,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="602" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="602" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A602" s="1">
         <v>46163</v>
       </c>
@@ -12516,7 +12517,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="603" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="603" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A603" s="1">
         <v>46163</v>
       </c>
@@ -12536,7 +12537,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="604" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="604" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A604" s="1">
         <v>46163</v>
       </c>
@@ -12556,7 +12557,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="605" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="605" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A605" s="1">
         <v>46163</v>
       </c>
@@ -12576,7 +12577,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="606" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="606" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A606" s="1">
         <v>46163</v>
       </c>
@@ -12596,7 +12597,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="607" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="607" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A607" s="1">
         <v>46163</v>
       </c>
@@ -12616,7 +12617,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="608" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="608" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A608" s="1">
         <v>46163</v>
       </c>
@@ -12636,7 +12637,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="609" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="609" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A609" s="1">
         <v>46163</v>
       </c>
@@ -12656,7 +12657,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="610" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="610" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A610" s="1">
         <v>46164</v>
       </c>
@@ -12676,7 +12677,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="611" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="611" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A611" s="1">
         <v>46164</v>
       </c>
@@ -12696,7 +12697,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="612" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="612" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A612" s="1">
         <v>46164</v>
       </c>
@@ -12716,7 +12717,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="613" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="613" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A613" s="1">
         <v>46164</v>
       </c>
@@ -12736,7 +12737,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="614" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="614" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A614" s="1">
         <v>46164</v>
       </c>
@@ -12756,7 +12757,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="615" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="615" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A615" s="1">
         <v>46164</v>
       </c>
@@ -12776,7 +12777,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="616" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="616" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A616" s="1">
         <v>46164</v>
       </c>
@@ -12796,7 +12797,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="617" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="617" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A617" s="1">
         <v>46164</v>
       </c>
@@ -12816,7 +12817,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="618" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="618" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A618" s="1">
         <v>46164</v>
       </c>
@@ -12836,7 +12837,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="619" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="619" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A619" s="1">
         <v>46164</v>
       </c>
@@ -12856,7 +12857,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="620" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="620" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A620" s="1">
         <v>46164</v>
       </c>
@@ -12876,7 +12877,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="621" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="621" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A621" s="1">
         <v>46164</v>
       </c>
@@ -12896,7 +12897,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="622" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="622" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A622" s="1">
         <v>46164</v>
       </c>
@@ -12916,7 +12917,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="623" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="623" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A623" s="1">
         <v>46164</v>
       </c>
@@ -12936,7 +12937,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="624" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="624" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A624" s="1">
         <v>46164</v>
       </c>
@@ -12956,7 +12957,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="625" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="625" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A625" s="1">
         <v>46165</v>
       </c>
@@ -12976,7 +12977,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="626" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="626" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A626" s="1">
         <v>46165</v>
       </c>
@@ -12996,7 +12997,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="627" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="627" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A627" s="1">
         <v>46165</v>
       </c>
@@ -13016,7 +13017,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="628" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="628" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A628" s="1">
         <v>46165</v>
       </c>
@@ -13036,7 +13037,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="629" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="629" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A629" s="1">
         <v>46165</v>
       </c>
@@ -13056,7 +13057,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="630" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="630" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A630" s="1">
         <v>46165</v>
       </c>
@@ -13076,7 +13077,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="631" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="631" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A631" s="1">
         <v>46165</v>
       </c>
@@ -13096,7 +13097,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="632" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="632" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A632" s="1">
         <v>46165</v>
       </c>
@@ -13116,7 +13117,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="633" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="633" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A633" s="1">
         <v>46165</v>
       </c>
@@ -13136,7 +13137,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="634" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="634" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A634" s="1">
         <v>46165</v>
       </c>
@@ -13156,7 +13157,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="635" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="635" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A635" s="1">
         <v>46165</v>
       </c>
@@ -13176,7 +13177,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="636" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="636" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A636" s="1">
         <v>46165</v>
       </c>
@@ -13196,7 +13197,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="637" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="637" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A637" s="1">
         <v>46165</v>
       </c>
@@ -13216,7 +13217,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="638" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="638" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A638" s="1">
         <v>46165</v>
       </c>
@@ -13236,7 +13237,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="639" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="639" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A639" s="1">
         <v>46165</v>
       </c>
@@ -13256,7 +13257,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="640" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="640" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A640" s="1">
         <v>46165</v>
       </c>
@@ -13276,7 +13277,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="641" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="641" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A641" s="1">
         <v>46166</v>
       </c>
@@ -13296,7 +13297,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="642" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="642" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A642" s="1">
         <v>46166</v>
       </c>
@@ -13316,7 +13317,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="643" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="643" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A643" s="1">
         <v>46166</v>
       </c>
@@ -13336,7 +13337,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="644" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="644" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A644" s="1">
         <v>46166</v>
       </c>
@@ -13356,7 +13357,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="645" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="645" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A645" s="1">
         <v>46166</v>
       </c>
@@ -13376,7 +13377,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="646" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="646" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A646" s="1">
         <v>46166</v>
       </c>
@@ -13396,7 +13397,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="647" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="647" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A647" s="1">
         <v>46166</v>
       </c>
@@ -13416,7 +13417,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="648" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="648" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A648" s="1">
         <v>46166</v>
       </c>
@@ -13436,7 +13437,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="649" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="649" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A649" s="1">
         <v>46166</v>
       </c>
@@ -13456,7 +13457,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="650" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="650" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A650" s="1">
         <v>46166</v>
       </c>
@@ -13476,7 +13477,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="651" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="651" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A651" s="1">
         <v>46166</v>
       </c>
@@ -13496,7 +13497,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="652" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="652" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A652" s="1">
         <v>46166</v>
       </c>
@@ -13516,7 +13517,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="653" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="653" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A653" s="1">
         <v>46166</v>
       </c>
@@ -13536,7 +13537,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="654" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="654" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A654" s="1">
         <v>46166</v>
       </c>
@@ -13556,7 +13557,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="655" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="655" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A655" s="1">
         <v>46166</v>
       </c>
@@ -13576,7 +13577,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="656" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="656" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A656" s="1">
         <v>46166</v>
       </c>
@@ -13596,7 +13597,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="657" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="657" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A657" s="1">
         <v>46167</v>
       </c>
@@ -13616,7 +13617,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="658" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="658" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A658" s="1">
         <v>46167</v>
       </c>
@@ -13636,7 +13637,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="659" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="659" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A659" s="1">
         <v>46167</v>
       </c>
@@ -13656,7 +13657,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="660" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="660" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A660" s="1">
         <v>46167</v>
       </c>
@@ -13676,7 +13677,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="661" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="661" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A661" s="1">
         <v>46167</v>
       </c>
@@ -13696,7 +13697,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="662" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="662" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A662" s="1">
         <v>46167</v>
       </c>
@@ -13716,7 +13717,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="663" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="663" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A663" s="1">
         <v>46167</v>
       </c>
@@ -13736,7 +13737,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="664" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="664" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A664" s="1">
         <v>46167</v>
       </c>
@@ -13756,7 +13757,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="665" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="665" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A665" s="1">
         <v>46167</v>
       </c>
@@ -13776,7 +13777,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="666" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="666" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A666" s="1">
         <v>46167</v>
       </c>
@@ -13796,7 +13797,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="667" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="667" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A667" s="1">
         <v>46167</v>
       </c>
@@ -13816,7 +13817,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="668" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="668" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A668" s="1">
         <v>46167</v>
       </c>
@@ -13836,7 +13837,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="669" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="669" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A669" s="1">
         <v>46167</v>
       </c>
@@ -13856,7 +13857,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="670" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="670" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A670" s="1">
         <v>46167</v>
       </c>
@@ -13876,7 +13877,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="671" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="671" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A671" s="1">
         <v>46167</v>
       </c>
@@ -13896,7 +13897,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="672" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="672" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A672" s="1">
         <v>46167</v>
       </c>
@@ -13916,7 +13917,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="673" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="673" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A673" s="1">
         <v>46168</v>
       </c>
@@ -13936,7 +13937,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="674" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="674" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A674" s="1">
         <v>46168</v>
       </c>
@@ -13956,7 +13957,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="675" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="675" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A675" s="1">
         <v>46168</v>
       </c>
@@ -13976,7 +13977,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="676" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="676" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A676" s="1">
         <v>46168</v>
       </c>
@@ -13996,7 +13997,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="677" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="677" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A677" s="1">
         <v>46168</v>
       </c>
@@ -14016,7 +14017,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="678" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="678" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A678" s="1">
         <v>46168</v>
       </c>
@@ -14036,7 +14037,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="679" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="679" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A679" s="1">
         <v>46168</v>
       </c>
@@ -14056,7 +14057,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="680" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="680" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A680" s="1">
         <v>46168</v>
       </c>
@@ -14076,7 +14077,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="681" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="681" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A681" s="1">
         <v>46168</v>
       </c>
@@ -14096,7 +14097,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="682" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="682" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A682" s="1">
         <v>46168</v>
       </c>
@@ -14116,7 +14117,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="683" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="683" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A683" s="1">
         <v>46168</v>
       </c>
@@ -14136,7 +14137,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="684" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="684" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A684" s="1">
         <v>46168</v>
       </c>
@@ -14156,7 +14157,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="685" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="685" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A685" s="1">
         <v>46168</v>
       </c>
@@ -14176,7 +14177,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="686" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="686" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A686" s="1">
         <v>46168</v>
       </c>
@@ -14196,7 +14197,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="687" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="687" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A687" s="1">
         <v>46168</v>
       </c>
@@ -14216,7 +14217,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="688" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="688" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A688" s="1">
         <v>46168</v>
       </c>
@@ -14236,7 +14237,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="689" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="689" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A689" s="1">
         <v>46168</v>
       </c>
@@ -14256,7 +14257,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="690" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="690" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A690" s="1">
         <v>46168</v>
       </c>
@@ -14276,7 +14277,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="691" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="691" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A691" s="1">
         <v>46169</v>
       </c>
@@ -14296,7 +14297,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="692" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="692" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A692" s="1">
         <v>46169</v>
       </c>
@@ -14316,7 +14317,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="693" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="693" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A693" s="1">
         <v>46169</v>
       </c>
@@ -14336,7 +14337,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="694" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="694" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A694" s="1">
         <v>46169</v>
       </c>
@@ -14356,7 +14357,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="695" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="695" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A695" s="1">
         <v>46169</v>
       </c>
@@ -14376,7 +14377,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="696" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="696" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A696" s="1">
         <v>46169</v>
       </c>
@@ -14396,7 +14397,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="697" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="697" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A697" s="1">
         <v>46169</v>
       </c>
@@ -14416,7 +14417,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="698" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="698" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A698" s="1">
         <v>46169</v>
       </c>
@@ -14436,7 +14437,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="699" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="699" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A699" s="1">
         <v>46169</v>
       </c>
@@ -14456,7 +14457,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="700" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="700" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A700" s="1">
         <v>46169</v>
       </c>
@@ -14476,7 +14477,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="701" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="701" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A701" s="1">
         <v>46169</v>
       </c>
@@ -14496,7 +14497,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="702" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="702" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A702" s="1">
         <v>46169</v>
       </c>
@@ -14516,7 +14517,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="703" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="703" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A703" s="1">
         <v>46169</v>
       </c>
@@ -14536,7 +14537,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="704" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="704" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A704" s="1">
         <v>46169</v>
       </c>
@@ -14556,7 +14557,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="705" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="705" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A705" s="1">
         <v>46169</v>
       </c>
@@ -14576,7 +14577,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="706" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="706" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A706" s="1">
         <v>46169</v>
       </c>
@@ -14596,7 +14597,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="707" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="707" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A707" s="1">
         <v>46169</v>
       </c>
@@ -14616,7 +14617,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="708" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="708" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A708" s="1">
         <v>46169</v>
       </c>
@@ -14636,7 +14637,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="709" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="709" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A709" s="1">
         <v>46170</v>
       </c>
@@ -14656,7 +14657,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="710" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="710" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A710" s="1">
         <v>46170</v>
       </c>
@@ -14676,7 +14677,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="711" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="711" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A711" s="1">
         <v>46170</v>
       </c>
@@ -14696,7 +14697,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="712" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="712" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A712" s="1">
         <v>46170</v>
       </c>
@@ -14716,7 +14717,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="713" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="713" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A713" s="1">
         <v>46170</v>
       </c>
@@ -14736,7 +14737,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="714" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="714" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A714" s="1">
         <v>46170</v>
       </c>
@@ -14756,7 +14757,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="715" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="715" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A715" s="1">
         <v>46170</v>
       </c>
@@ -14776,7 +14777,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="716" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="716" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A716" s="1">
         <v>46170</v>
       </c>
@@ -14796,7 +14797,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="717" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="717" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A717" s="1">
         <v>46170</v>
       </c>
@@ -14816,7 +14817,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="718" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="718" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A718" s="1">
         <v>46170</v>
       </c>
@@ -14836,7 +14837,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="719" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="719" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A719" s="1">
         <v>46170</v>
       </c>
@@ -14856,7 +14857,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="720" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="720" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A720" s="1">
         <v>46170</v>
       </c>
@@ -14876,7 +14877,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="721" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="721" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A721" s="1">
         <v>46170</v>
       </c>
@@ -14896,7 +14897,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="722" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="722" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A722" s="1">
         <v>46170</v>
       </c>
@@ -14916,7 +14917,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="723" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="723" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A723" s="1">
         <v>46170</v>
       </c>
@@ -14936,7 +14937,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="724" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="724" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A724" s="1">
         <v>46170</v>
       </c>
@@ -14956,7 +14957,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="725" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="725" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A725" s="1">
         <v>46170</v>
       </c>
@@ -14976,7 +14977,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="726" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="726" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A726" s="1">
         <v>46171</v>
       </c>
@@ -14996,7 +14997,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="727" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="727" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A727" s="1">
         <v>46171</v>
       </c>
@@ -15016,7 +15017,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="728" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="728" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A728" s="1">
         <v>46171</v>
       </c>
@@ -15036,7 +15037,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="729" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="729" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A729" s="1">
         <v>46171</v>
       </c>
@@ -15056,7 +15057,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="730" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="730" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A730" s="1">
         <v>46171</v>
       </c>
@@ -15076,7 +15077,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="731" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="731" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A731" s="1">
         <v>46171</v>
       </c>
@@ -15096,7 +15097,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="732" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="732" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A732" s="1">
         <v>46171</v>
       </c>
@@ -15116,7 +15117,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="733" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="733" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A733" s="1">
         <v>46171</v>
       </c>
@@ -15136,7 +15137,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="734" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="734" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A734" s="1">
         <v>46171</v>
       </c>
@@ -15156,7 +15157,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="735" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="735" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A735" s="1">
         <v>46171</v>
       </c>
@@ -15176,7 +15177,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="736" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="736" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A736" s="1">
         <v>46171</v>
       </c>
@@ -15196,7 +15197,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="737" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="737" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A737" s="1">
         <v>46171</v>
       </c>
@@ -15216,7 +15217,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="738" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="738" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A738" s="1">
         <v>46171</v>
       </c>
@@ -15236,7 +15237,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="739" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="739" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A739" s="1">
         <v>46171</v>
       </c>
@@ -15256,7 +15257,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="740" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="740" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A740" s="1">
         <v>46171</v>
       </c>
@@ -15276,7 +15277,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="741" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="741" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A741" s="1">
         <v>46171</v>
       </c>
@@ -15296,7 +15297,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="742" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="742" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A742" s="1">
         <v>46171</v>
       </c>
@@ -15316,7 +15317,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="743" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="743" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A743" s="1">
         <v>46171</v>
       </c>
@@ -15336,7 +15337,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="744" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="744" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A744" s="1">
         <v>46172</v>
       </c>
@@ -15356,7 +15357,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="745" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="745" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A745" s="1">
         <v>46172</v>
       </c>
@@ -15376,7 +15377,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="746" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="746" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A746" s="1">
         <v>46172</v>
       </c>
@@ -15396,7 +15397,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="747" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="747" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A747" s="1">
         <v>46172</v>
       </c>
@@ -15416,7 +15417,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="748" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="748" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A748" s="1">
         <v>46172</v>
       </c>
@@ -15436,7 +15437,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="749" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="749" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A749" s="1">
         <v>46172</v>
       </c>
@@ -15456,7 +15457,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="750" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="750" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A750" s="1">
         <v>46172</v>
       </c>
@@ -15476,7 +15477,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="751" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="751" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A751" s="1">
         <v>46172</v>
       </c>
@@ -15496,7 +15497,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="752" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="752" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A752" s="1">
         <v>46172</v>
       </c>
@@ -15516,7 +15517,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="753" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="753" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A753" s="1">
         <v>46172</v>
       </c>
@@ -15536,7 +15537,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="754" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="754" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A754" s="1">
         <v>46172</v>
       </c>
@@ -15556,7 +15557,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="755" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="755" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A755" s="1">
         <v>46172</v>
       </c>
@@ -15576,7 +15577,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="756" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="756" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A756" s="1">
         <v>46172</v>
       </c>
@@ -15596,7 +15597,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="757" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="757" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A757" s="1">
         <v>46172</v>
       </c>
@@ -15616,7 +15617,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="758" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="758" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A758" s="1">
         <v>46172</v>
       </c>
@@ -15636,7 +15637,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="759" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="759" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A759" s="1">
         <v>46172</v>
       </c>
@@ -15656,7 +15657,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="760" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="760" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A760" s="1">
         <v>46172</v>
       </c>
@@ -15676,7 +15677,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="761" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="761" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A761" s="1">
         <v>46172</v>
       </c>
@@ -15696,7 +15697,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="762" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="762" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A762" s="1">
         <v>46173</v>
       </c>
@@ -15716,7 +15717,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="763" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="763" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A763" s="1">
         <v>46173</v>
       </c>
@@ -15736,7 +15737,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="764" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="764" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A764" s="1">
         <v>46173</v>
       </c>
@@ -15756,7 +15757,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="765" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="765" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A765" s="1">
         <v>46173</v>
       </c>
@@ -15776,7 +15777,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="766" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="766" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A766" s="1">
         <v>46173</v>
       </c>
@@ -15796,7 +15797,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="767" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="767" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A767" s="1">
         <v>46173</v>
       </c>
@@ -15816,7 +15817,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="768" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="768" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A768" s="1">
         <v>46173</v>
       </c>
@@ -15836,7 +15837,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="769" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="769" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A769" s="1">
         <v>46173</v>
       </c>
@@ -15856,7 +15857,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="770" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="770" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A770" s="1">
         <v>46173</v>
       </c>
@@ -15876,7 +15877,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="771" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="771" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A771" s="1">
         <v>46173</v>
       </c>
@@ -15896,7 +15897,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="772" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="772" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A772" s="1">
         <v>46173</v>
       </c>
@@ -15916,7 +15917,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="773" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="773" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A773" s="1">
         <v>46173</v>
       </c>
@@ -15936,7 +15937,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="774" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="774" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A774" s="1">
         <v>46173</v>
       </c>
@@ -15956,7 +15957,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="775" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="775" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A775" s="1">
         <v>46173</v>
       </c>
@@ -15976,7 +15977,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="776" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="776" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A776" s="1">
         <v>46173</v>
       </c>
@@ -15996,7 +15997,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="777" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="777" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A777" s="1">
         <v>46173</v>
       </c>
@@ -18396,7 +18397,674 @@
         <v>10</v>
       </c>
     </row>
+    <row r="897" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A897" s="1">
+        <v>46181</v>
+      </c>
+      <c r="B897" t="s">
+        <v>5</v>
+      </c>
+      <c r="C897" t="s">
+        <v>17</v>
+      </c>
+      <c r="D897">
+        <v>10</v>
+      </c>
+      <c r="E897">
+        <v>7</v>
+      </c>
+      <c r="F897" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="898" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A898" s="1">
+        <v>46181</v>
+      </c>
+      <c r="B898" t="s">
+        <v>5</v>
+      </c>
+      <c r="C898" t="s">
+        <v>15</v>
+      </c>
+      <c r="D898">
+        <v>2</v>
+      </c>
+      <c r="E898">
+        <v>2</v>
+      </c>
+      <c r="F898" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="899" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A899" s="1">
+        <v>46181</v>
+      </c>
+      <c r="B899" t="s">
+        <v>5</v>
+      </c>
+      <c r="C899" t="s">
+        <v>16</v>
+      </c>
+      <c r="D899">
+        <v>3</v>
+      </c>
+      <c r="E899">
+        <v>2</v>
+      </c>
+      <c r="F899" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="900" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A900" s="1">
+        <v>46181</v>
+      </c>
+      <c r="B900" t="s">
+        <v>13</v>
+      </c>
+      <c r="C900" t="s">
+        <v>17</v>
+      </c>
+      <c r="D900">
+        <v>13</v>
+      </c>
+      <c r="E900">
+        <v>13</v>
+      </c>
+      <c r="F900" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="901" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A901" s="1">
+        <v>46181</v>
+      </c>
+      <c r="B901" t="s">
+        <v>13</v>
+      </c>
+      <c r="C901" t="s">
+        <v>15</v>
+      </c>
+      <c r="D901">
+        <v>3</v>
+      </c>
+      <c r="E901">
+        <v>3</v>
+      </c>
+      <c r="F901" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="902" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A902" s="1">
+        <v>46181</v>
+      </c>
+      <c r="B902" t="s">
+        <v>13</v>
+      </c>
+      <c r="C902" t="s">
+        <v>16</v>
+      </c>
+      <c r="D902">
+        <v>11</v>
+      </c>
+      <c r="E902">
+        <v>9</v>
+      </c>
+      <c r="F902" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="903" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A903" s="1">
+        <v>46181</v>
+      </c>
+      <c r="B903" t="s">
+        <v>12</v>
+      </c>
+      <c r="C903" t="s">
+        <v>17</v>
+      </c>
+      <c r="D903">
+        <v>8</v>
+      </c>
+      <c r="E903">
+        <v>8</v>
+      </c>
+      <c r="F903" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="904" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A904" s="1">
+        <v>46181</v>
+      </c>
+      <c r="B904" t="s">
+        <v>12</v>
+      </c>
+      <c r="C904" t="s">
+        <v>16</v>
+      </c>
+      <c r="D904">
+        <v>4</v>
+      </c>
+      <c r="E904">
+        <v>3</v>
+      </c>
+      <c r="F904" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="905" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A905" s="1">
+        <v>46181</v>
+      </c>
+      <c r="B905" t="s">
+        <v>7</v>
+      </c>
+      <c r="C905" t="s">
+        <v>17</v>
+      </c>
+      <c r="D905">
+        <v>11</v>
+      </c>
+      <c r="E905">
+        <v>11</v>
+      </c>
+      <c r="F905" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="906" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A906" s="1">
+        <v>46181</v>
+      </c>
+      <c r="B906" t="s">
+        <v>7</v>
+      </c>
+      <c r="C906" t="s">
+        <v>15</v>
+      </c>
+      <c r="D906">
+        <v>3</v>
+      </c>
+      <c r="E906">
+        <v>3</v>
+      </c>
+      <c r="F906" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="907" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A907" s="1">
+        <v>46181</v>
+      </c>
+      <c r="B907" t="s">
+        <v>7</v>
+      </c>
+      <c r="C907" t="s">
+        <v>16</v>
+      </c>
+      <c r="D907">
+        <v>9</v>
+      </c>
+      <c r="E907">
+        <v>6</v>
+      </c>
+      <c r="F907" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="908" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A908" s="1">
+        <v>46181</v>
+      </c>
+      <c r="B908" t="s">
+        <v>11</v>
+      </c>
+      <c r="C908" t="s">
+        <v>17</v>
+      </c>
+      <c r="D908">
+        <v>30</v>
+      </c>
+      <c r="E908">
+        <v>28</v>
+      </c>
+      <c r="F908" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="909" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A909" s="1">
+        <v>46181</v>
+      </c>
+      <c r="B909" t="s">
+        <v>11</v>
+      </c>
+      <c r="C909" t="s">
+        <v>15</v>
+      </c>
+      <c r="D909">
+        <v>3</v>
+      </c>
+      <c r="E909">
+        <v>3</v>
+      </c>
+      <c r="F909" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="910" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A910" s="1">
+        <v>46181</v>
+      </c>
+      <c r="B910" t="s">
+        <v>11</v>
+      </c>
+      <c r="C910" t="s">
+        <v>16</v>
+      </c>
+      <c r="D910">
+        <v>7</v>
+      </c>
+      <c r="E910">
+        <v>4</v>
+      </c>
+      <c r="F910" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="911" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A911" s="1">
+        <v>46181</v>
+      </c>
+      <c r="B911" t="s">
+        <v>9</v>
+      </c>
+      <c r="C911" t="s">
+        <v>17</v>
+      </c>
+      <c r="D911">
+        <v>21</v>
+      </c>
+      <c r="E911">
+        <v>21</v>
+      </c>
+      <c r="F911" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="912" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A912" s="1">
+        <v>46181</v>
+      </c>
+      <c r="B912" t="s">
+        <v>9</v>
+      </c>
+      <c r="C912" t="s">
+        <v>16</v>
+      </c>
+      <c r="D912">
+        <v>7</v>
+      </c>
+      <c r="E912">
+        <v>3</v>
+      </c>
+      <c r="F912" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="913" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A913" s="1">
+        <v>46182</v>
+      </c>
+      <c r="B913" t="s">
+        <v>5</v>
+      </c>
+      <c r="C913" t="s">
+        <v>17</v>
+      </c>
+      <c r="D913">
+        <v>11</v>
+      </c>
+      <c r="E913">
+        <v>11</v>
+      </c>
+      <c r="F913" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="914" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A914" s="1">
+        <v>46182</v>
+      </c>
+      <c r="B914" t="s">
+        <v>5</v>
+      </c>
+      <c r="C914" t="s">
+        <v>15</v>
+      </c>
+      <c r="D914">
+        <v>6</v>
+      </c>
+      <c r="E914">
+        <v>6</v>
+      </c>
+      <c r="F914" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="915" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A915" s="1">
+        <v>46182</v>
+      </c>
+      <c r="B915" t="s">
+        <v>5</v>
+      </c>
+      <c r="C915" t="s">
+        <v>16</v>
+      </c>
+      <c r="D915">
+        <v>10</v>
+      </c>
+      <c r="E915">
+        <v>5</v>
+      </c>
+      <c r="F915" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="916" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A916" s="1">
+        <v>46182</v>
+      </c>
+      <c r="B916" t="s">
+        <v>13</v>
+      </c>
+      <c r="C916" t="s">
+        <v>17</v>
+      </c>
+      <c r="D916">
+        <v>27</v>
+      </c>
+      <c r="E916">
+        <v>26</v>
+      </c>
+      <c r="F916" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="917" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A917" s="1">
+        <v>46182</v>
+      </c>
+      <c r="B917" t="s">
+        <v>13</v>
+      </c>
+      <c r="C917" t="s">
+        <v>15</v>
+      </c>
+      <c r="D917">
+        <v>14</v>
+      </c>
+      <c r="E917">
+        <v>9</v>
+      </c>
+      <c r="F917" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="918" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A918" s="1">
+        <v>46182</v>
+      </c>
+      <c r="B918" t="s">
+        <v>13</v>
+      </c>
+      <c r="C918" t="s">
+        <v>16</v>
+      </c>
+      <c r="D918">
+        <v>11</v>
+      </c>
+      <c r="E918">
+        <v>5</v>
+      </c>
+      <c r="F918" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="919" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A919" s="1">
+        <v>46182</v>
+      </c>
+      <c r="B919" t="s">
+        <v>12</v>
+      </c>
+      <c r="C919" t="s">
+        <v>17</v>
+      </c>
+      <c r="D919">
+        <v>12</v>
+      </c>
+      <c r="E919">
+        <v>12</v>
+      </c>
+      <c r="F919" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="920" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A920" s="1">
+        <v>46182</v>
+      </c>
+      <c r="B920" t="s">
+        <v>12</v>
+      </c>
+      <c r="C920" t="s">
+        <v>15</v>
+      </c>
+      <c r="D920">
+        <v>4</v>
+      </c>
+      <c r="E920">
+        <v>4</v>
+      </c>
+      <c r="F920" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="921" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A921" s="1">
+        <v>46182</v>
+      </c>
+      <c r="B921" t="s">
+        <v>7</v>
+      </c>
+      <c r="C921" t="s">
+        <v>17</v>
+      </c>
+      <c r="D921">
+        <v>5</v>
+      </c>
+      <c r="E921">
+        <v>5</v>
+      </c>
+      <c r="F921" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="922" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A922" s="1">
+        <v>46182</v>
+      </c>
+      <c r="B922" t="s">
+        <v>7</v>
+      </c>
+      <c r="C922" t="s">
+        <v>15</v>
+      </c>
+      <c r="D922">
+        <v>3</v>
+      </c>
+      <c r="E922">
+        <v>3</v>
+      </c>
+      <c r="F922" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="923" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A923" s="1">
+        <v>46182</v>
+      </c>
+      <c r="B923" t="s">
+        <v>7</v>
+      </c>
+      <c r="C923" t="s">
+        <v>16</v>
+      </c>
+      <c r="D923">
+        <v>2</v>
+      </c>
+      <c r="E923">
+        <v>2</v>
+      </c>
+      <c r="F923" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="924" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A924" s="1">
+        <v>46182</v>
+      </c>
+      <c r="B924" t="s">
+        <v>11</v>
+      </c>
+      <c r="C924" t="s">
+        <v>17</v>
+      </c>
+      <c r="D924">
+        <v>35</v>
+      </c>
+      <c r="E924">
+        <v>34</v>
+      </c>
+      <c r="F924" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="925" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A925" s="1">
+        <v>46182</v>
+      </c>
+      <c r="B925" t="s">
+        <v>11</v>
+      </c>
+      <c r="C925" t="s">
+        <v>15</v>
+      </c>
+      <c r="D925">
+        <v>4</v>
+      </c>
+      <c r="E925">
+        <v>4</v>
+      </c>
+      <c r="F925" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="926" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A926" s="1">
+        <v>46182</v>
+      </c>
+      <c r="B926" t="s">
+        <v>11</v>
+      </c>
+      <c r="C926" t="s">
+        <v>16</v>
+      </c>
+      <c r="D926">
+        <v>2</v>
+      </c>
+      <c r="E926">
+        <v>2</v>
+      </c>
+      <c r="F926" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="927" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A927" s="1">
+        <v>46182</v>
+      </c>
+      <c r="B927" t="s">
+        <v>9</v>
+      </c>
+      <c r="C927" t="s">
+        <v>17</v>
+      </c>
+      <c r="D927">
+        <v>17</v>
+      </c>
+      <c r="E927">
+        <v>16</v>
+      </c>
+      <c r="F927" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="928" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A928" s="1">
+        <v>46182</v>
+      </c>
+      <c r="B928" t="s">
+        <v>9</v>
+      </c>
+      <c r="C928" t="s">
+        <v>15</v>
+      </c>
+      <c r="D928">
+        <v>2</v>
+      </c>
+      <c r="E928">
+        <v>2</v>
+      </c>
+      <c r="F928" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="929" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A929" s="1">
+        <v>46182</v>
+      </c>
+      <c r="B929" t="s">
+        <v>9</v>
+      </c>
+      <c r="C929" t="s">
+        <v>16</v>
+      </c>
+      <c r="D929">
+        <v>7</v>
+      </c>
+      <c r="E929">
+        <v>5</v>
+      </c>
+      <c r="F929" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:F896" xr:uid="{22A7DA2E-DF85-4559-9E8B-F6EDBCD02D26}">
+    <filterColumn colId="0">
+      <filters>
+        <dateGroupItem year="2026" month="6" dateTimeGrouping="month"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Deepanshi Ahuja\Desktop\used_cars_dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55FA245F-E30C-4E3E-905B-B8390CA38ABC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C9B2E1C-8D51-4CB7-8C2C-D11C0A188D04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{D7CE9FC5-F49F-40D4-93B4-AA39BB343A99}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2790" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2892" uniqueCount="18">
   <si>
     <t>Date</t>
   </si>
@@ -469,7 +469,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22A7DA2E-DF85-4559-9E8B-F6EDBCD02D26}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:F929"/>
+  <dimension ref="A1:F963"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.08984375" bestFit="1" customWidth="1"/>
@@ -19054,6 +19054,686 @@
         <v>5</v>
       </c>
       <c r="F929" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="930" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A930" s="1">
+        <v>46183</v>
+      </c>
+      <c r="B930" t="s">
+        <v>5</v>
+      </c>
+      <c r="C930" t="s">
+        <v>17</v>
+      </c>
+      <c r="D930">
+        <v>9</v>
+      </c>
+      <c r="E930">
+        <v>9</v>
+      </c>
+      <c r="F930" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="931" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A931" s="1">
+        <v>46183</v>
+      </c>
+      <c r="B931" t="s">
+        <v>5</v>
+      </c>
+      <c r="C931" t="s">
+        <v>15</v>
+      </c>
+      <c r="D931">
+        <v>10</v>
+      </c>
+      <c r="E931">
+        <v>8</v>
+      </c>
+      <c r="F931" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="932" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A932" s="1">
+        <v>46183</v>
+      </c>
+      <c r="B932" t="s">
+        <v>5</v>
+      </c>
+      <c r="C932" t="s">
+        <v>16</v>
+      </c>
+      <c r="D932">
+        <v>8</v>
+      </c>
+      <c r="E932">
+        <v>8</v>
+      </c>
+      <c r="F932" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="933" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A933" s="1">
+        <v>46183</v>
+      </c>
+      <c r="B933" t="s">
+        <v>13</v>
+      </c>
+      <c r="C933" t="s">
+        <v>17</v>
+      </c>
+      <c r="D933">
+        <v>22</v>
+      </c>
+      <c r="E933">
+        <v>22</v>
+      </c>
+      <c r="F933" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="934" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A934" s="1">
+        <v>46183</v>
+      </c>
+      <c r="B934" t="s">
+        <v>13</v>
+      </c>
+      <c r="C934" t="s">
+        <v>15</v>
+      </c>
+      <c r="D934">
+        <v>11</v>
+      </c>
+      <c r="E934">
+        <v>11</v>
+      </c>
+      <c r="F934" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="935" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A935" s="1">
+        <v>46183</v>
+      </c>
+      <c r="B935" t="s">
+        <v>13</v>
+      </c>
+      <c r="C935" t="s">
+        <v>16</v>
+      </c>
+      <c r="D935">
+        <v>6</v>
+      </c>
+      <c r="E935">
+        <v>5</v>
+      </c>
+      <c r="F935" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="936" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A936" s="1">
+        <v>46183</v>
+      </c>
+      <c r="B936" t="s">
+        <v>12</v>
+      </c>
+      <c r="C936" t="s">
+        <v>17</v>
+      </c>
+      <c r="D936">
+        <v>11</v>
+      </c>
+      <c r="E936">
+        <v>11</v>
+      </c>
+      <c r="F936" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="937" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A937" s="1">
+        <v>46183</v>
+      </c>
+      <c r="B937" t="s">
+        <v>12</v>
+      </c>
+      <c r="C937" t="s">
+        <v>15</v>
+      </c>
+      <c r="D937">
+        <v>1</v>
+      </c>
+      <c r="E937">
+        <v>1</v>
+      </c>
+      <c r="F937" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="938" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A938" s="1">
+        <v>46183</v>
+      </c>
+      <c r="B938" t="s">
+        <v>12</v>
+      </c>
+      <c r="C938" t="s">
+        <v>16</v>
+      </c>
+      <c r="D938">
+        <v>6</v>
+      </c>
+      <c r="E938">
+        <v>3</v>
+      </c>
+      <c r="F938" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="939" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A939" s="1">
+        <v>46183</v>
+      </c>
+      <c r="B939" t="s">
+        <v>7</v>
+      </c>
+      <c r="C939" t="s">
+        <v>17</v>
+      </c>
+      <c r="D939">
+        <v>10</v>
+      </c>
+      <c r="E939">
+        <v>10</v>
+      </c>
+      <c r="F939" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="940" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A940" s="1">
+        <v>46183</v>
+      </c>
+      <c r="B940" t="s">
+        <v>7</v>
+      </c>
+      <c r="C940" t="s">
+        <v>15</v>
+      </c>
+      <c r="D940">
+        <v>5</v>
+      </c>
+      <c r="E940">
+        <v>4</v>
+      </c>
+      <c r="F940" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="941" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A941" s="1">
+        <v>46183</v>
+      </c>
+      <c r="B941" t="s">
+        <v>7</v>
+      </c>
+      <c r="C941" t="s">
+        <v>16</v>
+      </c>
+      <c r="D941">
+        <v>3</v>
+      </c>
+      <c r="E941">
+        <v>3</v>
+      </c>
+      <c r="F941" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="942" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A942" s="1">
+        <v>46183</v>
+      </c>
+      <c r="B942" t="s">
+        <v>11</v>
+      </c>
+      <c r="C942" t="s">
+        <v>17</v>
+      </c>
+      <c r="D942">
+        <v>15</v>
+      </c>
+      <c r="E942">
+        <v>15</v>
+      </c>
+      <c r="F942" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="943" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A943" s="1">
+        <v>46183</v>
+      </c>
+      <c r="B943" t="s">
+        <v>11</v>
+      </c>
+      <c r="C943" t="s">
+        <v>15</v>
+      </c>
+      <c r="D943">
+        <v>3</v>
+      </c>
+      <c r="E943">
+        <v>3</v>
+      </c>
+      <c r="F943" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="944" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A944" s="1">
+        <v>46183</v>
+      </c>
+      <c r="B944" t="s">
+        <v>11</v>
+      </c>
+      <c r="C944" t="s">
+        <v>16</v>
+      </c>
+      <c r="D944">
+        <v>6</v>
+      </c>
+      <c r="E944">
+        <v>3</v>
+      </c>
+      <c r="F944" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="945" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A945" s="1">
+        <v>46183</v>
+      </c>
+      <c r="B945" t="s">
+        <v>9</v>
+      </c>
+      <c r="C945" t="s">
+        <v>17</v>
+      </c>
+      <c r="D945">
+        <v>11</v>
+      </c>
+      <c r="E945">
+        <v>11</v>
+      </c>
+      <c r="F945" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="946" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A946" s="1">
+        <v>46183</v>
+      </c>
+      <c r="B946" t="s">
+        <v>9</v>
+      </c>
+      <c r="C946" t="s">
+        <v>16</v>
+      </c>
+      <c r="D946">
+        <v>7</v>
+      </c>
+      <c r="E946">
+        <v>6</v>
+      </c>
+      <c r="F946" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="947" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A947" s="1">
+        <v>46184</v>
+      </c>
+      <c r="B947" t="s">
+        <v>5</v>
+      </c>
+      <c r="C947" t="s">
+        <v>17</v>
+      </c>
+      <c r="D947">
+        <v>12</v>
+      </c>
+      <c r="E947">
+        <v>12</v>
+      </c>
+      <c r="F947" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="948" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A948" s="1">
+        <v>46184</v>
+      </c>
+      <c r="B948" t="s">
+        <v>5</v>
+      </c>
+      <c r="C948" t="s">
+        <v>15</v>
+      </c>
+      <c r="D948">
+        <v>3</v>
+      </c>
+      <c r="E948">
+        <v>3</v>
+      </c>
+      <c r="F948" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="949" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A949" s="1">
+        <v>46184</v>
+      </c>
+      <c r="B949" t="s">
+        <v>5</v>
+      </c>
+      <c r="C949" t="s">
+        <v>16</v>
+      </c>
+      <c r="D949">
+        <v>4</v>
+      </c>
+      <c r="E949">
+        <v>2</v>
+      </c>
+      <c r="F949" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="950" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A950" s="1">
+        <v>46184</v>
+      </c>
+      <c r="B950" t="s">
+        <v>13</v>
+      </c>
+      <c r="C950" t="s">
+        <v>17</v>
+      </c>
+      <c r="D950">
+        <v>19</v>
+      </c>
+      <c r="E950">
+        <v>19</v>
+      </c>
+      <c r="F950" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="951" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A951" s="1">
+        <v>46184</v>
+      </c>
+      <c r="B951" t="s">
+        <v>13</v>
+      </c>
+      <c r="C951" t="s">
+        <v>15</v>
+      </c>
+      <c r="D951">
+        <v>10</v>
+      </c>
+      <c r="E951">
+        <v>6</v>
+      </c>
+      <c r="F951" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="952" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A952" s="1">
+        <v>46184</v>
+      </c>
+      <c r="B952" t="s">
+        <v>13</v>
+      </c>
+      <c r="C952" t="s">
+        <v>16</v>
+      </c>
+      <c r="D952">
+        <v>14</v>
+      </c>
+      <c r="E952">
+        <v>9</v>
+      </c>
+      <c r="F952" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="953" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A953" s="1">
+        <v>46184</v>
+      </c>
+      <c r="B953" t="s">
+        <v>12</v>
+      </c>
+      <c r="C953" t="s">
+        <v>17</v>
+      </c>
+      <c r="D953">
+        <v>16</v>
+      </c>
+      <c r="E953">
+        <v>14</v>
+      </c>
+      <c r="F953" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="954" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A954" s="1">
+        <v>46184</v>
+      </c>
+      <c r="B954" t="s">
+        <v>12</v>
+      </c>
+      <c r="C954" t="s">
+        <v>16</v>
+      </c>
+      <c r="D954">
+        <v>1</v>
+      </c>
+      <c r="E954">
+        <v>1</v>
+      </c>
+      <c r="F954" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="955" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A955" s="1">
+        <v>46184</v>
+      </c>
+      <c r="B955" t="s">
+        <v>7</v>
+      </c>
+      <c r="C955" t="s">
+        <v>17</v>
+      </c>
+      <c r="D955">
+        <v>18</v>
+      </c>
+      <c r="E955">
+        <v>15</v>
+      </c>
+      <c r="F955" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="956" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A956" s="1">
+        <v>46184</v>
+      </c>
+      <c r="B956" t="s">
+        <v>7</v>
+      </c>
+      <c r="C956" t="s">
+        <v>15</v>
+      </c>
+      <c r="D956">
+        <v>9</v>
+      </c>
+      <c r="E956">
+        <v>9</v>
+      </c>
+      <c r="F956" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="957" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A957" s="1">
+        <v>46184</v>
+      </c>
+      <c r="B957" t="s">
+        <v>7</v>
+      </c>
+      <c r="C957" t="s">
+        <v>16</v>
+      </c>
+      <c r="D957">
+        <v>12</v>
+      </c>
+      <c r="E957">
+        <v>6</v>
+      </c>
+      <c r="F957" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="958" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A958" s="1">
+        <v>46184</v>
+      </c>
+      <c r="B958" t="s">
+        <v>11</v>
+      </c>
+      <c r="C958" t="s">
+        <v>17</v>
+      </c>
+      <c r="D958">
+        <v>46</v>
+      </c>
+      <c r="E958">
+        <v>43</v>
+      </c>
+      <c r="F958" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="959" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A959" s="1">
+        <v>46184</v>
+      </c>
+      <c r="B959" t="s">
+        <v>11</v>
+      </c>
+      <c r="C959" t="s">
+        <v>15</v>
+      </c>
+      <c r="D959">
+        <v>8</v>
+      </c>
+      <c r="E959">
+        <v>7</v>
+      </c>
+      <c r="F959" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="960" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A960" s="1">
+        <v>46184</v>
+      </c>
+      <c r="B960" t="s">
+        <v>11</v>
+      </c>
+      <c r="C960" t="s">
+        <v>16</v>
+      </c>
+      <c r="D960">
+        <v>9</v>
+      </c>
+      <c r="E960">
+        <v>5</v>
+      </c>
+      <c r="F960" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="961" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A961" s="1">
+        <v>46184</v>
+      </c>
+      <c r="B961" t="s">
+        <v>9</v>
+      </c>
+      <c r="C961" t="s">
+        <v>17</v>
+      </c>
+      <c r="D961">
+        <v>13</v>
+      </c>
+      <c r="E961">
+        <v>13</v>
+      </c>
+      <c r="F961" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="962" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A962" s="1">
+        <v>46184</v>
+      </c>
+      <c r="B962" t="s">
+        <v>9</v>
+      </c>
+      <c r="C962" t="s">
+        <v>15</v>
+      </c>
+      <c r="D962">
+        <v>1</v>
+      </c>
+      <c r="E962">
+        <v>1</v>
+      </c>
+      <c r="F962" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="963" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A963" s="1">
+        <v>46184</v>
+      </c>
+      <c r="B963" t="s">
+        <v>9</v>
+      </c>
+      <c r="C963" t="s">
+        <v>16</v>
+      </c>
+      <c r="D963">
+        <v>3</v>
+      </c>
+      <c r="E963">
+        <v>3</v>
+      </c>
+      <c r="F963" t="s">
         <v>10</v>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Deepanshi Ahuja\Desktop\used_cars_dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C9B2E1C-8D51-4CB7-8C2C-D11C0A188D04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6C637CD-AF15-47C9-80A7-1D736FB43092}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{D7CE9FC5-F49F-40D4-93B4-AA39BB343A99}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="data" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">data!$A$1:$F$896</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">data!$A$1:$F$963</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -468,7 +468,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22A7DA2E-DF85-4559-9E8B-F6EDBCD02D26}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:F963"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -497,7 +496,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>46115</v>
       </c>
@@ -517,7 +516,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>46117</v>
       </c>
@@ -537,7 +536,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>46118</v>
       </c>
@@ -557,7 +556,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>46119</v>
       </c>
@@ -577,7 +576,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>46119</v>
       </c>
@@ -597,7 +596,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>46119</v>
       </c>
@@ -617,7 +616,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>46120</v>
       </c>
@@ -637,7 +636,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>46120</v>
       </c>
@@ -657,7 +656,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>46120</v>
       </c>
@@ -677,7 +676,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>46120</v>
       </c>
@@ -697,7 +696,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>46120</v>
       </c>
@@ -717,7 +716,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <v>46120</v>
       </c>
@@ -737,7 +736,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <v>46120</v>
       </c>
@@ -757,7 +756,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <v>46121</v>
       </c>
@@ -777,7 +776,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <v>46121</v>
       </c>
@@ -797,7 +796,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="17" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <v>46121</v>
       </c>
@@ -817,7 +816,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="18" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
         <v>46121</v>
       </c>
@@ -837,7 +836,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
         <v>46121</v>
       </c>
@@ -857,7 +856,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
         <v>46121</v>
       </c>
@@ -877,7 +876,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="21" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
         <v>46121</v>
       </c>
@@ -897,7 +896,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
         <v>46122</v>
       </c>
@@ -917,7 +916,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="23" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
         <v>46122</v>
       </c>
@@ -937,7 +936,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="24" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
         <v>46122</v>
       </c>
@@ -957,7 +956,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="25" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
         <v>46122</v>
       </c>
@@ -977,7 +976,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="26" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
         <v>46122</v>
       </c>
@@ -997,7 +996,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="27" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
         <v>46122</v>
       </c>
@@ -1017,7 +1016,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="28" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
         <v>46122</v>
       </c>
@@ -1037,7 +1036,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="29" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" s="1">
         <v>46122</v>
       </c>
@@ -1057,7 +1056,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="30" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30" s="1">
         <v>46123</v>
       </c>
@@ -1077,7 +1076,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="31" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31" s="1">
         <v>46123</v>
       </c>
@@ -1097,7 +1096,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="32" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32" s="1">
         <v>46123</v>
       </c>
@@ -1117,7 +1116,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="33" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33" s="1">
         <v>46123</v>
       </c>
@@ -1137,7 +1136,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="34" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34" s="1">
         <v>46123</v>
       </c>
@@ -1157,7 +1156,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="35" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35" s="1">
         <v>46123</v>
       </c>
@@ -1177,7 +1176,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="36" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A36" s="1">
         <v>46123</v>
       </c>
@@ -1197,7 +1196,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="37" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A37" s="1">
         <v>46123</v>
       </c>
@@ -1217,7 +1216,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="38" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A38" s="1">
         <v>46124</v>
       </c>
@@ -1237,7 +1236,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="39" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A39" s="1">
         <v>46124</v>
       </c>
@@ -1257,7 +1256,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="40" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40" s="1">
         <v>46124</v>
       </c>
@@ -1277,7 +1276,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="41" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A41" s="1">
         <v>46124</v>
       </c>
@@ -1297,7 +1296,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="42" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A42" s="1">
         <v>46124</v>
       </c>
@@ -1317,7 +1316,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="43" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A43" s="1">
         <v>46124</v>
       </c>
@@ -1337,7 +1336,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="44" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A44" s="1">
         <v>46124</v>
       </c>
@@ -1357,7 +1356,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="45" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A45" s="1">
         <v>46124</v>
       </c>
@@ -1377,7 +1376,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="46" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A46" s="1">
         <v>46124</v>
       </c>
@@ -1397,7 +1396,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="47" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A47" s="1">
         <v>46125</v>
       </c>
@@ -1417,7 +1416,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="48" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A48" s="1">
         <v>46125</v>
       </c>
@@ -1437,7 +1436,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="49" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A49" s="1">
         <v>46125</v>
       </c>
@@ -1457,7 +1456,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="50" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A50" s="1">
         <v>46125</v>
       </c>
@@ -1477,7 +1476,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="51" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A51" s="1">
         <v>46125</v>
       </c>
@@ -1497,7 +1496,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="52" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A52" s="1">
         <v>46125</v>
       </c>
@@ -1517,7 +1516,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="53" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A53" s="1">
         <v>46125</v>
       </c>
@@ -1537,7 +1536,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="54" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A54" s="1">
         <v>46125</v>
       </c>
@@ -1557,7 +1556,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="55" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A55" s="1">
         <v>46125</v>
       </c>
@@ -1577,7 +1576,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="56" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A56" s="1">
         <v>46126</v>
       </c>
@@ -1597,7 +1596,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="57" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A57" s="1">
         <v>46126</v>
       </c>
@@ -1617,7 +1616,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="58" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A58" s="1">
         <v>46126</v>
       </c>
@@ -1637,7 +1636,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="59" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A59" s="1">
         <v>46126</v>
       </c>
@@ -1657,7 +1656,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="60" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A60" s="1">
         <v>46126</v>
       </c>
@@ -1677,7 +1676,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="61" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A61" s="1">
         <v>46126</v>
       </c>
@@ -1697,7 +1696,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="62" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A62" s="1">
         <v>46126</v>
       </c>
@@ -1717,7 +1716,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="63" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A63" s="1">
         <v>46126</v>
       </c>
@@ -1737,7 +1736,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="64" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A64" s="1">
         <v>46126</v>
       </c>
@@ -1757,7 +1756,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="65" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A65" s="1">
         <v>46126</v>
       </c>
@@ -1777,7 +1776,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="66" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A66" s="1">
         <v>46127</v>
       </c>
@@ -1797,7 +1796,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="67" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A67" s="1">
         <v>46127</v>
       </c>
@@ -1817,7 +1816,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="68" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A68" s="1">
         <v>46127</v>
       </c>
@@ -1837,7 +1836,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="69" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A69" s="1">
         <v>46127</v>
       </c>
@@ -1857,7 +1856,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="70" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A70" s="1">
         <v>46127</v>
       </c>
@@ -1877,7 +1876,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="71" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A71" s="1">
         <v>46127</v>
       </c>
@@ -1897,7 +1896,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="72" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A72" s="1">
         <v>46127</v>
       </c>
@@ -1917,7 +1916,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="73" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A73" s="1">
         <v>46127</v>
       </c>
@@ -1937,7 +1936,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="74" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A74" s="1">
         <v>46127</v>
       </c>
@@ -1957,7 +1956,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="75" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A75" s="1">
         <v>46128</v>
       </c>
@@ -1977,7 +1976,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="76" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A76" s="1">
         <v>46128</v>
       </c>
@@ -1997,7 +1996,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="77" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A77" s="1">
         <v>46128</v>
       </c>
@@ -2017,7 +2016,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="78" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A78" s="1">
         <v>46128</v>
       </c>
@@ -2037,7 +2036,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="79" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A79" s="1">
         <v>46128</v>
       </c>
@@ -2057,7 +2056,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="80" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A80" s="1">
         <v>46128</v>
       </c>
@@ -2077,7 +2076,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="81" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A81" s="1">
         <v>46128</v>
       </c>
@@ -2097,7 +2096,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="82" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A82" s="1">
         <v>46128</v>
       </c>
@@ -2117,7 +2116,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="83" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A83" s="1">
         <v>46128</v>
       </c>
@@ -2137,7 +2136,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="84" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A84" s="1">
         <v>46129</v>
       </c>
@@ -2157,7 +2156,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="85" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A85" s="1">
         <v>46129</v>
       </c>
@@ -2177,7 +2176,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="86" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A86" s="1">
         <v>46129</v>
       </c>
@@ -2197,7 +2196,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="87" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A87" s="1">
         <v>46129</v>
       </c>
@@ -2217,7 +2216,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="88" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A88" s="1">
         <v>46129</v>
       </c>
@@ -2237,7 +2236,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="89" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A89" s="1">
         <v>46129</v>
       </c>
@@ -2257,7 +2256,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="90" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A90" s="1">
         <v>46129</v>
       </c>
@@ -2277,7 +2276,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="91" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A91" s="1">
         <v>46129</v>
       </c>
@@ -2297,7 +2296,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="92" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A92" s="1">
         <v>46130</v>
       </c>
@@ -2317,7 +2316,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="93" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A93" s="1">
         <v>46130</v>
       </c>
@@ -2337,7 +2336,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="94" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A94" s="1">
         <v>46130</v>
       </c>
@@ -2357,7 +2356,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="95" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A95" s="1">
         <v>46130</v>
       </c>
@@ -2377,7 +2376,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="96" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A96" s="1">
         <v>46130</v>
       </c>
@@ -2397,7 +2396,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="97" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A97" s="1">
         <v>46130</v>
       </c>
@@ -2417,7 +2416,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="98" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A98" s="1">
         <v>46130</v>
       </c>
@@ -2437,7 +2436,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="99" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A99" s="1">
         <v>46130</v>
       </c>
@@ -2457,7 +2456,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="100" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A100" s="1">
         <v>46130</v>
       </c>
@@ -2477,7 +2476,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="101" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A101" s="1">
         <v>46131</v>
       </c>
@@ -2497,7 +2496,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="102" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A102" s="1">
         <v>46131</v>
       </c>
@@ -2517,7 +2516,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="103" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A103" s="1">
         <v>46131</v>
       </c>
@@ -2537,7 +2536,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="104" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A104" s="1">
         <v>46131</v>
       </c>
@@ -2557,7 +2556,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="105" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A105" s="1">
         <v>46131</v>
       </c>
@@ -2577,7 +2576,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="106" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A106" s="1">
         <v>46131</v>
       </c>
@@ -2597,7 +2596,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="107" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A107" s="1">
         <v>46131</v>
       </c>
@@ -2617,7 +2616,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="108" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A108" s="1">
         <v>46131</v>
       </c>
@@ -2637,7 +2636,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="109" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A109" s="1">
         <v>46132</v>
       </c>
@@ -2657,7 +2656,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="110" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A110" s="1">
         <v>46132</v>
       </c>
@@ -2677,7 +2676,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="111" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A111" s="1">
         <v>46132</v>
       </c>
@@ -2697,7 +2696,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="112" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A112" s="1">
         <v>46132</v>
       </c>
@@ -2717,7 +2716,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="113" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A113" s="1">
         <v>46132</v>
       </c>
@@ -2737,7 +2736,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="114" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A114" s="1">
         <v>46132</v>
       </c>
@@ -2757,7 +2756,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="115" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A115" s="1">
         <v>46132</v>
       </c>
@@ -2777,7 +2776,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="116" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A116" s="1">
         <v>46132</v>
       </c>
@@ -2797,7 +2796,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="117" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A117" s="1">
         <v>46132</v>
       </c>
@@ -2817,7 +2816,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="118" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A118" s="1">
         <v>46132</v>
       </c>
@@ -2837,7 +2836,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="119" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A119" s="1">
         <v>46132</v>
       </c>
@@ -2857,7 +2856,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="120" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A120" s="1">
         <v>46132</v>
       </c>
@@ -2877,7 +2876,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="121" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A121" s="1">
         <v>46133</v>
       </c>
@@ -2897,7 +2896,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="122" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A122" s="1">
         <v>46133</v>
       </c>
@@ -2917,7 +2916,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="123" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A123" s="1">
         <v>46133</v>
       </c>
@@ -2937,7 +2936,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="124" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A124" s="1">
         <v>46133</v>
       </c>
@@ -2957,7 +2956,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="125" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A125" s="1">
         <v>46133</v>
       </c>
@@ -2977,7 +2976,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="126" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A126" s="1">
         <v>46133</v>
       </c>
@@ -2997,7 +2996,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="127" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A127" s="1">
         <v>46133</v>
       </c>
@@ -3017,7 +3016,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="128" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A128" s="1">
         <v>46133</v>
       </c>
@@ -3037,7 +3036,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="129" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A129" s="1">
         <v>46133</v>
       </c>
@@ -3057,7 +3056,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="130" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A130" s="1">
         <v>46133</v>
       </c>
@@ -3077,7 +3076,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="131" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A131" s="1">
         <v>46133</v>
       </c>
@@ -3097,7 +3096,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="132" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A132" s="1">
         <v>46133</v>
       </c>
@@ -3117,7 +3116,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="133" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A133" s="1">
         <v>46134</v>
       </c>
@@ -3137,7 +3136,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="134" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A134" s="1">
         <v>46134</v>
       </c>
@@ -3157,7 +3156,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="135" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A135" s="1">
         <v>46134</v>
       </c>
@@ -3177,7 +3176,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="136" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A136" s="1">
         <v>46134</v>
       </c>
@@ -3197,7 +3196,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="137" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A137" s="1">
         <v>46134</v>
       </c>
@@ -3217,7 +3216,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="138" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A138" s="1">
         <v>46134</v>
       </c>
@@ -3237,7 +3236,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="139" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A139" s="1">
         <v>46134</v>
       </c>
@@ -3257,7 +3256,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="140" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A140" s="1">
         <v>46134</v>
       </c>
@@ -3277,7 +3276,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="141" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A141" s="1">
         <v>46134</v>
       </c>
@@ -3297,7 +3296,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="142" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A142" s="1">
         <v>46134</v>
       </c>
@@ -3317,7 +3316,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="143" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A143" s="1">
         <v>46134</v>
       </c>
@@ -3337,7 +3336,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="144" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A144" s="1">
         <v>46134</v>
       </c>
@@ -3357,7 +3356,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="145" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A145" s="1">
         <v>46134</v>
       </c>
@@ -3377,7 +3376,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="146" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A146" s="1">
         <v>46134</v>
       </c>
@@ -3397,7 +3396,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="147" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A147" s="1">
         <v>46135</v>
       </c>
@@ -3417,7 +3416,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="148" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A148" s="1">
         <v>46135</v>
       </c>
@@ -3437,7 +3436,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="149" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A149" s="1">
         <v>46135</v>
       </c>
@@ -3457,7 +3456,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="150" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A150" s="1">
         <v>46135</v>
       </c>
@@ -3477,7 +3476,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="151" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A151" s="1">
         <v>46135</v>
       </c>
@@ -3497,7 +3496,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="152" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A152" s="1">
         <v>46135</v>
       </c>
@@ -3517,7 +3516,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="153" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A153" s="1">
         <v>46135</v>
       </c>
@@ -3537,7 +3536,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="154" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A154" s="1">
         <v>46135</v>
       </c>
@@ -3557,7 +3556,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="155" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A155" s="1">
         <v>46135</v>
       </c>
@@ -3577,7 +3576,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="156" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A156" s="1">
         <v>46135</v>
       </c>
@@ -3597,7 +3596,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="157" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A157" s="1">
         <v>46135</v>
       </c>
@@ -3617,7 +3616,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="158" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A158" s="1">
         <v>46135</v>
       </c>
@@ -3637,7 +3636,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="159" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A159" s="1">
         <v>46135</v>
       </c>
@@ -3657,7 +3656,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="160" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A160" s="1">
         <v>46136</v>
       </c>
@@ -3677,7 +3676,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="161" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A161" s="1">
         <v>46136</v>
       </c>
@@ -3697,7 +3696,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="162" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A162" s="1">
         <v>46136</v>
       </c>
@@ -3717,7 +3716,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="163" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A163" s="1">
         <v>46136</v>
       </c>
@@ -3737,7 +3736,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="164" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A164" s="1">
         <v>46136</v>
       </c>
@@ -3757,7 +3756,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="165" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A165" s="1">
         <v>46136</v>
       </c>
@@ -3777,7 +3776,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="166" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A166" s="1">
         <v>46136</v>
       </c>
@@ -3797,7 +3796,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="167" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A167" s="1">
         <v>46136</v>
       </c>
@@ -3817,7 +3816,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="168" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A168" s="1">
         <v>46136</v>
       </c>
@@ -3837,7 +3836,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="169" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A169" s="1">
         <v>46136</v>
       </c>
@@ -3857,7 +3856,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="170" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A170" s="1">
         <v>46136</v>
       </c>
@@ -3877,7 +3876,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="171" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A171" s="1">
         <v>46136</v>
       </c>
@@ -3897,7 +3896,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="172" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A172" s="1">
         <v>46137</v>
       </c>
@@ -3917,7 +3916,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="173" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A173" s="1">
         <v>46137</v>
       </c>
@@ -3937,7 +3936,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="174" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A174" s="1">
         <v>46137</v>
       </c>
@@ -3957,7 +3956,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="175" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A175" s="1">
         <v>46137</v>
       </c>
@@ -3977,7 +3976,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="176" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A176" s="1">
         <v>46137</v>
       </c>
@@ -3997,7 +3996,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="177" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A177" s="1">
         <v>46137</v>
       </c>
@@ -4017,7 +4016,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="178" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A178" s="1">
         <v>46137</v>
       </c>
@@ -4037,7 +4036,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="179" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A179" s="1">
         <v>46137</v>
       </c>
@@ -4057,7 +4056,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="180" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A180" s="1">
         <v>46137</v>
       </c>
@@ -4077,7 +4076,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="181" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A181" s="1">
         <v>46137</v>
       </c>
@@ -4097,7 +4096,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="182" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A182" s="1">
         <v>46137</v>
       </c>
@@ -4117,7 +4116,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="183" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A183" s="1">
         <v>46137</v>
       </c>
@@ -4137,7 +4136,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="184" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A184" s="1">
         <v>46137</v>
       </c>
@@ -4157,7 +4156,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="185" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A185" s="1">
         <v>46137</v>
       </c>
@@ -4177,7 +4176,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="186" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A186" s="1">
         <v>46137</v>
       </c>
@@ -4197,7 +4196,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="187" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A187" s="1">
         <v>46137</v>
       </c>
@@ -4217,7 +4216,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="188" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A188" s="1">
         <v>46138</v>
       </c>
@@ -4237,7 +4236,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="189" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A189" s="1">
         <v>46138</v>
       </c>
@@ -4257,7 +4256,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="190" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A190" s="1">
         <v>46138</v>
       </c>
@@ -4277,7 +4276,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="191" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A191" s="1">
         <v>46138</v>
       </c>
@@ -4297,7 +4296,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="192" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A192" s="1">
         <v>46138</v>
       </c>
@@ -4317,7 +4316,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="193" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A193" s="1">
         <v>46138</v>
       </c>
@@ -4337,7 +4336,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="194" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A194" s="1">
         <v>46138</v>
       </c>
@@ -4357,7 +4356,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="195" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A195" s="1">
         <v>46138</v>
       </c>
@@ -4377,7 +4376,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="196" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A196" s="1">
         <v>46138</v>
       </c>
@@ -4397,7 +4396,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="197" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A197" s="1">
         <v>46138</v>
       </c>
@@ -4417,7 +4416,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="198" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A198" s="1">
         <v>46138</v>
       </c>
@@ -4437,7 +4436,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="199" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A199" s="1">
         <v>46138</v>
       </c>
@@ -4457,7 +4456,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="200" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A200" s="1">
         <v>46138</v>
       </c>
@@ -4477,7 +4476,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="201" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A201" s="1">
         <v>46138</v>
       </c>
@@ -4497,7 +4496,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="202" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A202" s="1">
         <v>46138</v>
       </c>
@@ -4517,7 +4516,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="203" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A203" s="1">
         <v>46138</v>
       </c>
@@ -4537,7 +4536,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="204" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A204" s="1">
         <v>46139</v>
       </c>
@@ -4557,7 +4556,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="205" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A205" s="1">
         <v>46139</v>
       </c>
@@ -4577,7 +4576,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="206" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A206" s="1">
         <v>46139</v>
       </c>
@@ -4597,7 +4596,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="207" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A207" s="1">
         <v>46139</v>
       </c>
@@ -4617,7 +4616,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="208" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A208" s="1">
         <v>46139</v>
       </c>
@@ -4637,7 +4636,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="209" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A209" s="1">
         <v>46139</v>
       </c>
@@ -4657,7 +4656,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="210" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A210" s="1">
         <v>46139</v>
       </c>
@@ -4677,7 +4676,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="211" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A211" s="1">
         <v>46139</v>
       </c>
@@ -4697,7 +4696,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="212" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A212" s="1">
         <v>46139</v>
       </c>
@@ -4717,7 +4716,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="213" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A213" s="1">
         <v>46139</v>
       </c>
@@ -4737,7 +4736,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="214" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A214" s="1">
         <v>46139</v>
       </c>
@@ -4757,7 +4756,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="215" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A215" s="1">
         <v>46139</v>
       </c>
@@ -4777,7 +4776,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="216" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A216" s="1">
         <v>46139</v>
       </c>
@@ -4797,7 +4796,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="217" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A217" s="1">
         <v>46139</v>
       </c>
@@ -4817,7 +4816,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="218" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A218" s="1">
         <v>46139</v>
       </c>
@@ -4837,7 +4836,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="219" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A219" s="1">
         <v>46139</v>
       </c>
@@ -4857,7 +4856,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="220" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A220" s="1">
         <v>46139</v>
       </c>
@@ -4877,7 +4876,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="221" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A221" s="1">
         <v>46140</v>
       </c>
@@ -4897,7 +4896,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="222" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A222" s="1">
         <v>46140</v>
       </c>
@@ -4917,7 +4916,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="223" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A223" s="1">
         <v>46140</v>
       </c>
@@ -4937,7 +4936,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="224" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A224" s="1">
         <v>46140</v>
       </c>
@@ -4957,7 +4956,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="225" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A225" s="1">
         <v>46140</v>
       </c>
@@ -4977,7 +4976,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="226" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A226" s="1">
         <v>46140</v>
       </c>
@@ -4997,7 +4996,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="227" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A227" s="1">
         <v>46140</v>
       </c>
@@ -5017,7 +5016,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="228" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A228" s="1">
         <v>46140</v>
       </c>
@@ -5037,7 +5036,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="229" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A229" s="1">
         <v>46140</v>
       </c>
@@ -5057,7 +5056,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="230" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A230" s="1">
         <v>46140</v>
       </c>
@@ -5077,7 +5076,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="231" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A231" s="1">
         <v>46140</v>
       </c>
@@ -5097,7 +5096,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="232" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A232" s="1">
         <v>46140</v>
       </c>
@@ -5117,7 +5116,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="233" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A233" s="1">
         <v>46140</v>
       </c>
@@ -5137,7 +5136,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="234" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A234" s="1">
         <v>46140</v>
       </c>
@@ -5157,7 +5156,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="235" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A235" s="1">
         <v>46140</v>
       </c>
@@ -5177,7 +5176,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="236" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A236" s="1">
         <v>46140</v>
       </c>
@@ -5197,7 +5196,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="237" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A237" s="1">
         <v>46140</v>
       </c>
@@ -5217,7 +5216,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="238" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A238" s="1">
         <v>46141</v>
       </c>
@@ -5237,7 +5236,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="239" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A239" s="1">
         <v>46141</v>
       </c>
@@ -5257,7 +5256,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="240" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A240" s="1">
         <v>46141</v>
       </c>
@@ -5277,7 +5276,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="241" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A241" s="1">
         <v>46141</v>
       </c>
@@ -5297,7 +5296,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="242" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A242" s="1">
         <v>46141</v>
       </c>
@@ -5317,7 +5316,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="243" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A243" s="1">
         <v>46141</v>
       </c>
@@ -5337,7 +5336,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="244" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A244" s="1">
         <v>46141</v>
       </c>
@@ -5357,7 +5356,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="245" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A245" s="1">
         <v>46141</v>
       </c>
@@ -5377,7 +5376,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="246" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A246" s="1">
         <v>46141</v>
       </c>
@@ -5397,7 +5396,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="247" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A247" s="1">
         <v>46141</v>
       </c>
@@ -5417,7 +5416,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="248" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A248" s="1">
         <v>46141</v>
       </c>
@@ -5437,7 +5436,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="249" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A249" s="1">
         <v>46141</v>
       </c>
@@ -5457,7 +5456,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="250" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A250" s="1">
         <v>46141</v>
       </c>
@@ -5477,7 +5476,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="251" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A251" s="1">
         <v>46141</v>
       </c>
@@ -5497,7 +5496,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="252" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A252" s="1">
         <v>46141</v>
       </c>
@@ -5517,7 +5516,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="253" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A253" s="1">
         <v>46141</v>
       </c>
@@ -5537,7 +5536,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="254" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A254" s="1">
         <v>46142</v>
       </c>
@@ -5557,7 +5556,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="255" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A255" s="1">
         <v>46142</v>
       </c>
@@ -5577,7 +5576,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="256" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A256" s="1">
         <v>46142</v>
       </c>
@@ -5597,7 +5596,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="257" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A257" s="1">
         <v>46142</v>
       </c>
@@ -5617,7 +5616,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="258" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A258" s="1">
         <v>46142</v>
       </c>
@@ -5637,7 +5636,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="259" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A259" s="1">
         <v>46142</v>
       </c>
@@ -5657,7 +5656,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="260" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A260" s="1">
         <v>46142</v>
       </c>
@@ -5677,7 +5676,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="261" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A261" s="1">
         <v>46142</v>
       </c>
@@ -5697,7 +5696,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="262" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A262" s="1">
         <v>46142</v>
       </c>
@@ -5717,7 +5716,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="263" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A263" s="1">
         <v>46142</v>
       </c>
@@ -5737,7 +5736,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="264" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A264" s="1">
         <v>46142</v>
       </c>
@@ -5757,7 +5756,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="265" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A265" s="1">
         <v>46142</v>
       </c>
@@ -5777,7 +5776,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="266" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A266" s="1">
         <v>46142</v>
       </c>
@@ -5797,7 +5796,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="267" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A267" s="1">
         <v>46142</v>
       </c>
@@ -5817,7 +5816,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="268" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A268" s="1">
         <v>46142</v>
       </c>
@@ -5837,7 +5836,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="269" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A269" s="1">
         <v>46142</v>
       </c>
@@ -5857,7 +5856,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="270" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A270" s="1">
         <v>46143</v>
       </c>
@@ -5877,7 +5876,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="271" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A271" s="1">
         <v>46143</v>
       </c>
@@ -5897,7 +5896,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="272" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A272" s="1">
         <v>46143</v>
       </c>
@@ -5917,7 +5916,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="273" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A273" s="1">
         <v>46143</v>
       </c>
@@ -5937,7 +5936,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="274" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A274" s="1">
         <v>46143</v>
       </c>
@@ -5957,7 +5956,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="275" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A275" s="1">
         <v>46143</v>
       </c>
@@ -5977,7 +5976,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="276" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A276" s="1">
         <v>46143</v>
       </c>
@@ -5997,7 +5996,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="277" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A277" s="1">
         <v>46143</v>
       </c>
@@ -6017,7 +6016,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="278" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A278" s="1">
         <v>46143</v>
       </c>
@@ -6037,7 +6036,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="279" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A279" s="1">
         <v>46143</v>
       </c>
@@ -6057,7 +6056,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="280" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A280" s="1">
         <v>46143</v>
       </c>
@@ -6077,7 +6076,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="281" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A281" s="1">
         <v>46143</v>
       </c>
@@ -6097,7 +6096,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="282" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A282" s="1">
         <v>46143</v>
       </c>
@@ -6117,7 +6116,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="283" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A283" s="1">
         <v>46143</v>
       </c>
@@ -6137,7 +6136,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="284" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A284" s="1">
         <v>46143</v>
       </c>
@@ -6157,7 +6156,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="285" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A285" s="1">
         <v>46143</v>
       </c>
@@ -6177,7 +6176,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="286" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A286" s="1">
         <v>46144</v>
       </c>
@@ -6197,7 +6196,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="287" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A287" s="1">
         <v>46144</v>
       </c>
@@ -6217,7 +6216,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="288" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A288" s="1">
         <v>46144</v>
       </c>
@@ -6237,7 +6236,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="289" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A289" s="1">
         <v>46144</v>
       </c>
@@ -6257,7 +6256,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="290" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A290" s="1">
         <v>46144</v>
       </c>
@@ -6277,7 +6276,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="291" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A291" s="1">
         <v>46144</v>
       </c>
@@ -6297,7 +6296,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="292" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A292" s="1">
         <v>46144</v>
       </c>
@@ -6317,7 +6316,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="293" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A293" s="1">
         <v>46144</v>
       </c>
@@ -6337,7 +6336,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="294" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A294" s="1">
         <v>46144</v>
       </c>
@@ -6357,7 +6356,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="295" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A295" s="1">
         <v>46144</v>
       </c>
@@ -6377,7 +6376,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="296" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A296" s="1">
         <v>46144</v>
       </c>
@@ -6397,7 +6396,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="297" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A297" s="1">
         <v>46144</v>
       </c>
@@ -6417,7 +6416,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="298" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A298" s="1">
         <v>46144</v>
       </c>
@@ -6437,7 +6436,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="299" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A299" s="1">
         <v>46144</v>
       </c>
@@ -6457,7 +6456,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="300" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A300" s="1">
         <v>46144</v>
       </c>
@@ -6477,7 +6476,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="301" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A301" s="1">
         <v>46144</v>
       </c>
@@ -6497,7 +6496,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="302" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A302" s="1">
         <v>46144</v>
       </c>
@@ -6517,7 +6516,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="303" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A303" s="1">
         <v>46145</v>
       </c>
@@ -6537,7 +6536,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="304" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A304" s="1">
         <v>46145</v>
       </c>
@@ -6557,7 +6556,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="305" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A305" s="1">
         <v>46145</v>
       </c>
@@ -6577,7 +6576,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="306" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A306" s="1">
         <v>46145</v>
       </c>
@@ -6597,7 +6596,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="307" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A307" s="1">
         <v>46145</v>
       </c>
@@ -6617,7 +6616,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="308" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A308" s="1">
         <v>46145</v>
       </c>
@@ -6637,7 +6636,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="309" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A309" s="1">
         <v>46145</v>
       </c>
@@ -6657,7 +6656,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="310" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A310" s="1">
         <v>46145</v>
       </c>
@@ -6677,7 +6676,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="311" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A311" s="1">
         <v>46145</v>
       </c>
@@ -6697,7 +6696,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="312" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A312" s="1">
         <v>46145</v>
       </c>
@@ -6717,7 +6716,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="313" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A313" s="1">
         <v>46145</v>
       </c>
@@ -6737,7 +6736,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="314" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A314" s="1">
         <v>46145</v>
       </c>
@@ -6757,7 +6756,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="315" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A315" s="1">
         <v>46145</v>
       </c>
@@ -6777,7 +6776,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="316" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A316" s="1">
         <v>46145</v>
       </c>
@@ -6797,7 +6796,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="317" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A317" s="1">
         <v>46146</v>
       </c>
@@ -6817,7 +6816,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="318" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A318" s="1">
         <v>46146</v>
       </c>
@@ -6837,7 +6836,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="319" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A319" s="1">
         <v>46146</v>
       </c>
@@ -6857,7 +6856,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="320" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A320" s="1">
         <v>46146</v>
       </c>
@@ -6877,7 +6876,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="321" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A321" s="1">
         <v>46146</v>
       </c>
@@ -6897,7 +6896,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="322" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A322" s="1">
         <v>46146</v>
       </c>
@@ -6917,7 +6916,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="323" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A323" s="1">
         <v>46146</v>
       </c>
@@ -6937,7 +6936,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="324" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A324" s="1">
         <v>46146</v>
       </c>
@@ -6957,7 +6956,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="325" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A325" s="1">
         <v>46146</v>
       </c>
@@ -6977,7 +6976,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="326" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A326" s="1">
         <v>46146</v>
       </c>
@@ -6997,7 +6996,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="327" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A327" s="1">
         <v>46146</v>
       </c>
@@ -7017,7 +7016,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="328" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A328" s="1">
         <v>46146</v>
       </c>
@@ -7037,7 +7036,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="329" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A329" s="1">
         <v>46146</v>
       </c>
@@ -7057,7 +7056,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="330" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A330" s="1">
         <v>46146</v>
       </c>
@@ -7077,7 +7076,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="331" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A331" s="1">
         <v>46146</v>
       </c>
@@ -7097,7 +7096,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="332" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A332" s="1">
         <v>46146</v>
       </c>
@@ -7117,7 +7116,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="333" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A333" s="1">
         <v>46147</v>
       </c>
@@ -7137,7 +7136,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="334" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A334" s="1">
         <v>46147</v>
       </c>
@@ -7157,7 +7156,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="335" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A335" s="1">
         <v>46147</v>
       </c>
@@ -7177,7 +7176,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="336" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A336" s="1">
         <v>46147</v>
       </c>
@@ -7197,7 +7196,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="337" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A337" s="1">
         <v>46147</v>
       </c>
@@ -7217,7 +7216,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="338" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A338" s="1">
         <v>46147</v>
       </c>
@@ -7237,7 +7236,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="339" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A339" s="1">
         <v>46147</v>
       </c>
@@ -7257,7 +7256,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="340" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A340" s="1">
         <v>46147</v>
       </c>
@@ -7277,7 +7276,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="341" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A341" s="1">
         <v>46147</v>
       </c>
@@ -7297,7 +7296,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="342" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A342" s="1">
         <v>46147</v>
       </c>
@@ -7317,7 +7316,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="343" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A343" s="1">
         <v>46147</v>
       </c>
@@ -7337,7 +7336,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="344" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A344" s="1">
         <v>46147</v>
       </c>
@@ -7357,7 +7356,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="345" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A345" s="1">
         <v>46147</v>
       </c>
@@ -7377,7 +7376,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="346" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A346" s="1">
         <v>46147</v>
       </c>
@@ -7397,7 +7396,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="347" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A347" s="1">
         <v>46147</v>
       </c>
@@ -7417,7 +7416,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="348" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A348" s="1">
         <v>46147</v>
       </c>
@@ -7437,7 +7436,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="349" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A349" s="1">
         <v>46147</v>
       </c>
@@ -7457,7 +7456,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="350" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A350" s="1">
         <v>46148</v>
       </c>
@@ -7477,7 +7476,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="351" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A351" s="1">
         <v>46148</v>
       </c>
@@ -7497,7 +7496,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="352" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A352" s="1">
         <v>46148</v>
       </c>
@@ -7517,7 +7516,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="353" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A353" s="1">
         <v>46148</v>
       </c>
@@ -7537,7 +7536,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="354" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A354" s="1">
         <v>46148</v>
       </c>
@@ -7557,7 +7556,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="355" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A355" s="1">
         <v>46148</v>
       </c>
@@ -7577,7 +7576,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="356" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A356" s="1">
         <v>46148</v>
       </c>
@@ -7597,7 +7596,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="357" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A357" s="1">
         <v>46148</v>
       </c>
@@ -7617,7 +7616,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="358" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A358" s="1">
         <v>46148</v>
       </c>
@@ -7637,7 +7636,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="359" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A359" s="1">
         <v>46148</v>
       </c>
@@ -7657,7 +7656,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="360" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A360" s="1">
         <v>46148</v>
       </c>
@@ -7677,7 +7676,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="361" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A361" s="1">
         <v>46148</v>
       </c>
@@ -7697,7 +7696,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="362" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A362" s="1">
         <v>46148</v>
       </c>
@@ -7717,7 +7716,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="363" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A363" s="1">
         <v>46148</v>
       </c>
@@ -7737,7 +7736,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="364" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A364" s="1">
         <v>46148</v>
       </c>
@@ -7757,7 +7756,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="365" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A365" s="1">
         <v>46149</v>
       </c>
@@ -7777,7 +7776,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="366" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A366" s="1">
         <v>46149</v>
       </c>
@@ -7797,7 +7796,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="367" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A367" s="1">
         <v>46149</v>
       </c>
@@ -7817,7 +7816,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="368" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A368" s="1">
         <v>46149</v>
       </c>
@@ -7837,7 +7836,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="369" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A369" s="1">
         <v>46149</v>
       </c>
@@ -7857,7 +7856,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="370" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A370" s="1">
         <v>46149</v>
       </c>
@@ -7877,7 +7876,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="371" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A371" s="1">
         <v>46149</v>
       </c>
@@ -7897,7 +7896,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="372" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A372" s="1">
         <v>46149</v>
       </c>
@@ -7917,7 +7916,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="373" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A373" s="1">
         <v>46149</v>
       </c>
@@ -7937,7 +7936,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="374" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A374" s="1">
         <v>46149</v>
       </c>
@@ -7957,7 +7956,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="375" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A375" s="1">
         <v>46149</v>
       </c>
@@ -7977,7 +7976,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="376" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A376" s="1">
         <v>46149</v>
       </c>
@@ -7997,7 +7996,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="377" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A377" s="1">
         <v>46149</v>
       </c>
@@ -8017,7 +8016,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="378" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A378" s="1">
         <v>46149</v>
       </c>
@@ -8037,7 +8036,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="379" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A379" s="1">
         <v>46149</v>
       </c>
@@ -8057,7 +8056,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="380" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A380" s="1">
         <v>46149</v>
       </c>
@@ -8077,7 +8076,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="381" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A381" s="1">
         <v>46150</v>
       </c>
@@ -8097,7 +8096,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="382" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A382" s="1">
         <v>46150</v>
       </c>
@@ -8117,7 +8116,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="383" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="383" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A383" s="1">
         <v>46150</v>
       </c>
@@ -8137,7 +8136,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="384" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A384" s="1">
         <v>46150</v>
       </c>
@@ -8157,7 +8156,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="385" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A385" s="1">
         <v>46150</v>
       </c>
@@ -8177,7 +8176,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="386" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="386" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A386" s="1">
         <v>46150</v>
       </c>
@@ -8197,7 +8196,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="387" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="387" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A387" s="1">
         <v>46150</v>
       </c>
@@ -8217,7 +8216,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="388" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="388" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A388" s="1">
         <v>46150</v>
       </c>
@@ -8237,7 +8236,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="389" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="389" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A389" s="1">
         <v>46150</v>
       </c>
@@ -8257,7 +8256,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="390" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="390" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A390" s="1">
         <v>46150</v>
       </c>
@@ -8277,7 +8276,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="391" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="391" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A391" s="1">
         <v>46150</v>
       </c>
@@ -8297,7 +8296,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="392" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="392" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A392" s="1">
         <v>46150</v>
       </c>
@@ -8317,7 +8316,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="393" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="393" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A393" s="1">
         <v>46150</v>
       </c>
@@ -8337,7 +8336,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="394" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="394" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A394" s="1">
         <v>46150</v>
       </c>
@@ -8357,7 +8356,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="395" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="395" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A395" s="1">
         <v>46150</v>
       </c>
@@ -8377,7 +8376,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="396" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="396" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A396" s="1">
         <v>46150</v>
       </c>
@@ -8397,7 +8396,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="397" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="397" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A397" s="1">
         <v>46151</v>
       </c>
@@ -8417,7 +8416,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="398" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="398" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A398" s="1">
         <v>46151</v>
       </c>
@@ -8437,7 +8436,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="399" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="399" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A399" s="1">
         <v>46151</v>
       </c>
@@ -8457,7 +8456,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="400" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="400" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A400" s="1">
         <v>46151</v>
       </c>
@@ -8477,7 +8476,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="401" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="401" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A401" s="1">
         <v>46151</v>
       </c>
@@ -8497,7 +8496,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="402" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="402" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A402" s="1">
         <v>46151</v>
       </c>
@@ -8517,7 +8516,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="403" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="403" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A403" s="1">
         <v>46151</v>
       </c>
@@ -8537,7 +8536,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="404" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="404" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A404" s="1">
         <v>46151</v>
       </c>
@@ -8557,7 +8556,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="405" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="405" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A405" s="1">
         <v>46151</v>
       </c>
@@ -8577,7 +8576,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="406" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="406" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A406" s="1">
         <v>46151</v>
       </c>
@@ -8597,7 +8596,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="407" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="407" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A407" s="1">
         <v>46151</v>
       </c>
@@ -8617,7 +8616,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="408" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="408" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A408" s="1">
         <v>46151</v>
       </c>
@@ -8637,7 +8636,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="409" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="409" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A409" s="1">
         <v>46151</v>
       </c>
@@ -8657,7 +8656,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="410" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="410" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A410" s="1">
         <v>46151</v>
       </c>
@@ -8677,7 +8676,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="411" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="411" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A411" s="1">
         <v>46151</v>
       </c>
@@ -8697,7 +8696,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="412" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="412" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A412" s="1">
         <v>46151</v>
       </c>
@@ -8717,7 +8716,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="413" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="413" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A413" s="1">
         <v>46152</v>
       </c>
@@ -8737,7 +8736,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="414" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="414" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A414" s="1">
         <v>46152</v>
       </c>
@@ -8757,7 +8756,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="415" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="415" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A415" s="1">
         <v>46152</v>
       </c>
@@ -8777,7 +8776,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="416" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="416" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A416" s="1">
         <v>46152</v>
       </c>
@@ -8797,7 +8796,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="417" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="417" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A417" s="1">
         <v>46152</v>
       </c>
@@ -8817,7 +8816,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="418" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="418" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A418" s="1">
         <v>46152</v>
       </c>
@@ -8837,7 +8836,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="419" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="419" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A419" s="1">
         <v>46152</v>
       </c>
@@ -8857,7 +8856,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="420" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="420" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A420" s="1">
         <v>46152</v>
       </c>
@@ -8877,7 +8876,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="421" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="421" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A421" s="1">
         <v>46152</v>
       </c>
@@ -8897,7 +8896,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="422" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="422" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A422" s="1">
         <v>46152</v>
       </c>
@@ -8917,7 +8916,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="423" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="423" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A423" s="1">
         <v>46152</v>
       </c>
@@ -8937,7 +8936,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="424" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="424" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A424" s="1">
         <v>46152</v>
       </c>
@@ -8957,7 +8956,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="425" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="425" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A425" s="1">
         <v>46152</v>
       </c>
@@ -8977,7 +8976,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="426" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="426" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A426" s="1">
         <v>46152</v>
       </c>
@@ -8997,7 +8996,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="427" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="427" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A427" s="1">
         <v>46152</v>
       </c>
@@ -9017,7 +9016,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="428" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="428" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A428" s="1">
         <v>46153</v>
       </c>
@@ -9037,7 +9036,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="429" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="429" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A429" s="1">
         <v>46153</v>
       </c>
@@ -9057,7 +9056,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="430" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="430" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A430" s="1">
         <v>46153</v>
       </c>
@@ -9077,7 +9076,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="431" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="431" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A431" s="1">
         <v>46153</v>
       </c>
@@ -9097,7 +9096,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="432" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="432" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A432" s="1">
         <v>46153</v>
       </c>
@@ -9117,7 +9116,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="433" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="433" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A433" s="1">
         <v>46153</v>
       </c>
@@ -9137,7 +9136,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="434" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="434" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A434" s="1">
         <v>46153</v>
       </c>
@@ -9157,7 +9156,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="435" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="435" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A435" s="1">
         <v>46153</v>
       </c>
@@ -9177,7 +9176,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="436" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="436" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A436" s="1">
         <v>46153</v>
       </c>
@@ -9197,7 +9196,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="437" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="437" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A437" s="1">
         <v>46153</v>
       </c>
@@ -9217,7 +9216,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="438" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="438" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A438" s="1">
         <v>46153</v>
       </c>
@@ -9237,7 +9236,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="439" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="439" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A439" s="1">
         <v>46153</v>
       </c>
@@ -9257,7 +9256,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="440" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="440" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A440" s="1">
         <v>46153</v>
       </c>
@@ -9277,7 +9276,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="441" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="441" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A441" s="1">
         <v>46153</v>
       </c>
@@ -9297,7 +9296,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="442" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="442" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A442" s="1">
         <v>46153</v>
       </c>
@@ -9317,7 +9316,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="443" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="443" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A443" s="1">
         <v>46153</v>
       </c>
@@ -9337,7 +9336,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="444" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="444" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A444" s="1">
         <v>46154</v>
       </c>
@@ -9357,7 +9356,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="445" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="445" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A445" s="1">
         <v>46154</v>
       </c>
@@ -9377,7 +9376,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="446" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="446" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A446" s="1">
         <v>46154</v>
       </c>
@@ -9397,7 +9396,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="447" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="447" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A447" s="1">
         <v>46154</v>
       </c>
@@ -9417,7 +9416,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="448" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="448" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A448" s="1">
         <v>46154</v>
       </c>
@@ -9437,7 +9436,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="449" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="449" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A449" s="1">
         <v>46154</v>
       </c>
@@ -9457,7 +9456,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="450" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="450" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A450" s="1">
         <v>46154</v>
       </c>
@@ -9477,7 +9476,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="451" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="451" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A451" s="1">
         <v>46154</v>
       </c>
@@ -9497,7 +9496,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="452" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="452" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A452" s="1">
         <v>46154</v>
       </c>
@@ -9517,7 +9516,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="453" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="453" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A453" s="1">
         <v>46154</v>
       </c>
@@ -9537,7 +9536,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="454" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="454" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A454" s="1">
         <v>46154</v>
       </c>
@@ -9557,7 +9556,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="455" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="455" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A455" s="1">
         <v>46154</v>
       </c>
@@ -9577,7 +9576,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="456" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="456" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A456" s="1">
         <v>46154</v>
       </c>
@@ -9597,7 +9596,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="457" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="457" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A457" s="1">
         <v>46154</v>
       </c>
@@ -9617,7 +9616,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="458" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="458" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A458" s="1">
         <v>46154</v>
       </c>
@@ -9637,7 +9636,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="459" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="459" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A459" s="1">
         <v>46154</v>
       </c>
@@ -9657,7 +9656,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="460" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="460" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A460" s="1">
         <v>46155</v>
       </c>
@@ -9677,7 +9676,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="461" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="461" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A461" s="1">
         <v>46155</v>
       </c>
@@ -9697,7 +9696,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="462" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="462" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A462" s="1">
         <v>46155</v>
       </c>
@@ -9717,7 +9716,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="463" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="463" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A463" s="1">
         <v>46155</v>
       </c>
@@ -9737,7 +9736,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="464" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="464" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A464" s="1">
         <v>46155</v>
       </c>
@@ -9757,7 +9756,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="465" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="465" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A465" s="1">
         <v>46155</v>
       </c>
@@ -9777,7 +9776,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="466" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="466" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A466" s="1">
         <v>46155</v>
       </c>
@@ -9797,7 +9796,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="467" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="467" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A467" s="1">
         <v>46155</v>
       </c>
@@ -9817,7 +9816,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="468" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="468" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A468" s="1">
         <v>46155</v>
       </c>
@@ -9837,7 +9836,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="469" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="469" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A469" s="1">
         <v>46155</v>
       </c>
@@ -9857,7 +9856,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="470" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="470" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A470" s="1">
         <v>46155</v>
       </c>
@@ -9877,7 +9876,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="471" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="471" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A471" s="1">
         <v>46155</v>
       </c>
@@ -9897,7 +9896,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="472" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="472" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A472" s="1">
         <v>46155</v>
       </c>
@@ -9917,7 +9916,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="473" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="473" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A473" s="1">
         <v>46155</v>
       </c>
@@ -9937,7 +9936,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="474" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="474" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A474" s="1">
         <v>46155</v>
       </c>
@@ -9957,7 +9956,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="475" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="475" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A475" s="1">
         <v>46155</v>
       </c>
@@ -9977,7 +9976,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="476" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="476" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A476" s="1">
         <v>46156</v>
       </c>
@@ -9997,7 +9996,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="477" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="477" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A477" s="1">
         <v>46156</v>
       </c>
@@ -10017,7 +10016,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="478" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="478" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A478" s="1">
         <v>46156</v>
       </c>
@@ -10037,7 +10036,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="479" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="479" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A479" s="1">
         <v>46156</v>
       </c>
@@ -10057,7 +10056,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="480" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="480" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A480" s="1">
         <v>46156</v>
       </c>
@@ -10077,7 +10076,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="481" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="481" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A481" s="1">
         <v>46156</v>
       </c>
@@ -10097,7 +10096,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="482" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="482" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A482" s="1">
         <v>46156</v>
       </c>
@@ -10117,7 +10116,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="483" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="483" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A483" s="1">
         <v>46156</v>
       </c>
@@ -10137,7 +10136,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="484" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="484" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A484" s="1">
         <v>46156</v>
       </c>
@@ -10157,7 +10156,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="485" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="485" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A485" s="1">
         <v>46156</v>
       </c>
@@ -10177,7 +10176,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="486" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="486" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A486" s="1">
         <v>46156</v>
       </c>
@@ -10197,7 +10196,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="487" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="487" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A487" s="1">
         <v>46156</v>
       </c>
@@ -10217,7 +10216,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="488" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="488" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A488" s="1">
         <v>46156</v>
       </c>
@@ -10237,7 +10236,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="489" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="489" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A489" s="1">
         <v>46156</v>
       </c>
@@ -10257,7 +10256,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="490" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="490" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A490" s="1">
         <v>46156</v>
       </c>
@@ -10277,7 +10276,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="491" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="491" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A491" s="1">
         <v>46156</v>
       </c>
@@ -10297,7 +10296,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="492" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="492" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A492" s="1">
         <v>46157</v>
       </c>
@@ -10317,7 +10316,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="493" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="493" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A493" s="1">
         <v>46157</v>
       </c>
@@ -10337,7 +10336,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="494" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="494" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A494" s="1">
         <v>46157</v>
       </c>
@@ -10357,7 +10356,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="495" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="495" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A495" s="1">
         <v>46157</v>
       </c>
@@ -10377,7 +10376,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="496" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="496" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A496" s="1">
         <v>46157</v>
       </c>
@@ -10397,7 +10396,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="497" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="497" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A497" s="1">
         <v>46157</v>
       </c>
@@ -10417,7 +10416,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="498" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="498" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A498" s="1">
         <v>46157</v>
       </c>
@@ -10437,7 +10436,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="499" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="499" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A499" s="1">
         <v>46157</v>
       </c>
@@ -10457,7 +10456,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="500" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="500" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A500" s="1">
         <v>46157</v>
       </c>
@@ -10477,7 +10476,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="501" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="501" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A501" s="1">
         <v>46157</v>
       </c>
@@ -10497,7 +10496,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="502" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="502" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A502" s="1">
         <v>46157</v>
       </c>
@@ -10517,7 +10516,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="503" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="503" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A503" s="1">
         <v>46157</v>
       </c>
@@ -10537,7 +10536,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="504" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="504" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A504" s="1">
         <v>46157</v>
       </c>
@@ -10557,7 +10556,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="505" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="505" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A505" s="1">
         <v>46157</v>
       </c>
@@ -10577,7 +10576,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="506" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="506" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A506" s="1">
         <v>46157</v>
       </c>
@@ -10597,7 +10596,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="507" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="507" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A507" s="1">
         <v>46157</v>
       </c>
@@ -10617,7 +10616,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="508" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="508" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A508" s="1">
         <v>46157</v>
       </c>
@@ -10637,7 +10636,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="509" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="509" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A509" s="1">
         <v>46157</v>
       </c>
@@ -10657,7 +10656,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="510" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="510" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A510" s="1">
         <v>46158</v>
       </c>
@@ -10677,7 +10676,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="511" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="511" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A511" s="1">
         <v>46158</v>
       </c>
@@ -10697,7 +10696,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="512" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="512" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A512" s="1">
         <v>46158</v>
       </c>
@@ -10717,7 +10716,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="513" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="513" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A513" s="1">
         <v>46158</v>
       </c>
@@ -10737,7 +10736,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="514" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="514" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A514" s="1">
         <v>46158</v>
       </c>
@@ -10757,7 +10756,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="515" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="515" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A515" s="1">
         <v>46158</v>
       </c>
@@ -10777,7 +10776,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="516" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="516" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A516" s="1">
         <v>46158</v>
       </c>
@@ -10797,7 +10796,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="517" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="517" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A517" s="1">
         <v>46158</v>
       </c>
@@ -10817,7 +10816,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="518" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="518" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A518" s="1">
         <v>46158</v>
       </c>
@@ -10837,7 +10836,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="519" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="519" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A519" s="1">
         <v>46158</v>
       </c>
@@ -10857,7 +10856,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="520" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="520" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A520" s="1">
         <v>46158</v>
       </c>
@@ -10877,7 +10876,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="521" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="521" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A521" s="1">
         <v>46158</v>
       </c>
@@ -10897,7 +10896,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="522" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="522" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A522" s="1">
         <v>46158</v>
       </c>
@@ -10917,7 +10916,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="523" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="523" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A523" s="1">
         <v>46158</v>
       </c>
@@ -10937,7 +10936,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="524" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="524" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A524" s="1">
         <v>46158</v>
       </c>
@@ -10957,7 +10956,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="525" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="525" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A525" s="1">
         <v>46158</v>
       </c>
@@ -10977,7 +10976,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="526" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="526" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A526" s="1">
         <v>46158</v>
       </c>
@@ -10997,7 +10996,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="527" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="527" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A527" s="1">
         <v>46159</v>
       </c>
@@ -11017,7 +11016,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="528" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="528" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A528" s="1">
         <v>46159</v>
       </c>
@@ -11037,7 +11036,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="529" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="529" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A529" s="1">
         <v>46159</v>
       </c>
@@ -11057,7 +11056,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="530" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="530" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A530" s="1">
         <v>46159</v>
       </c>
@@ -11077,7 +11076,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="531" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="531" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A531" s="1">
         <v>46159</v>
       </c>
@@ -11097,7 +11096,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="532" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="532" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A532" s="1">
         <v>46159</v>
       </c>
@@ -11117,7 +11116,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="533" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="533" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A533" s="1">
         <v>46159</v>
       </c>
@@ -11137,7 +11136,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="534" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="534" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A534" s="1">
         <v>46159</v>
       </c>
@@ -11157,7 +11156,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="535" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="535" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A535" s="1">
         <v>46159</v>
       </c>
@@ -11177,7 +11176,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="536" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="536" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A536" s="1">
         <v>46159</v>
       </c>
@@ -11197,7 +11196,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="537" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="537" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A537" s="1">
         <v>46159</v>
       </c>
@@ -11217,7 +11216,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="538" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="538" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A538" s="1">
         <v>46159</v>
       </c>
@@ -11237,7 +11236,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="539" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="539" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A539" s="1">
         <v>46159</v>
       </c>
@@ -11257,7 +11256,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="540" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="540" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A540" s="1">
         <v>46159</v>
       </c>
@@ -11277,7 +11276,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="541" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="541" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A541" s="1">
         <v>46159</v>
       </c>
@@ -11297,7 +11296,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="542" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="542" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A542" s="1">
         <v>46159</v>
       </c>
@@ -11317,7 +11316,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="543" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="543" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A543" s="1">
         <v>46159</v>
       </c>
@@ -11337,7 +11336,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="544" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="544" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A544" s="1">
         <v>46159</v>
       </c>
@@ -11357,7 +11356,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="545" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="545" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A545" s="1">
         <v>46160</v>
       </c>
@@ -11377,7 +11376,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="546" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="546" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A546" s="1">
         <v>46160</v>
       </c>
@@ -11397,7 +11396,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="547" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="547" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A547" s="1">
         <v>46160</v>
       </c>
@@ -11417,7 +11416,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="548" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="548" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A548" s="1">
         <v>46160</v>
       </c>
@@ -11437,7 +11436,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="549" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="549" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A549" s="1">
         <v>46160</v>
       </c>
@@ -11457,7 +11456,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="550" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="550" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A550" s="1">
         <v>46160</v>
       </c>
@@ -11477,7 +11476,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="551" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="551" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A551" s="1">
         <v>46160</v>
       </c>
@@ -11497,7 +11496,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="552" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="552" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A552" s="1">
         <v>46160</v>
       </c>
@@ -11517,7 +11516,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="553" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="553" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A553" s="1">
         <v>46160</v>
       </c>
@@ -11537,7 +11536,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="554" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="554" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A554" s="1">
         <v>46160</v>
       </c>
@@ -11557,7 +11556,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="555" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="555" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A555" s="1">
         <v>46160</v>
       </c>
@@ -11577,7 +11576,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="556" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="556" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A556" s="1">
         <v>46160</v>
       </c>
@@ -11597,7 +11596,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="557" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="557" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A557" s="1">
         <v>46160</v>
       </c>
@@ -11617,7 +11616,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="558" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="558" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A558" s="1">
         <v>46160</v>
       </c>
@@ -11637,7 +11636,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="559" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="559" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A559" s="1">
         <v>46160</v>
       </c>
@@ -11657,7 +11656,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="560" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="560" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A560" s="1">
         <v>46160</v>
       </c>
@@ -11677,7 +11676,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="561" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="561" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A561" s="1">
         <v>46160</v>
       </c>
@@ -11697,7 +11696,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="562" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="562" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A562" s="1">
         <v>46161</v>
       </c>
@@ -11717,7 +11716,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="563" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="563" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A563" s="1">
         <v>46161</v>
       </c>
@@ -11737,7 +11736,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="564" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="564" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A564" s="1">
         <v>46161</v>
       </c>
@@ -11757,7 +11756,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="565" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="565" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A565" s="1">
         <v>46161</v>
       </c>
@@ -11777,7 +11776,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="566" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="566" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A566" s="1">
         <v>46161</v>
       </c>
@@ -11797,7 +11796,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="567" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="567" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A567" s="1">
         <v>46161</v>
       </c>
@@ -11817,7 +11816,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="568" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="568" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A568" s="1">
         <v>46161</v>
       </c>
@@ -11837,7 +11836,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="569" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="569" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A569" s="1">
         <v>46161</v>
       </c>
@@ -11857,7 +11856,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="570" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="570" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A570" s="1">
         <v>46161</v>
       </c>
@@ -11877,7 +11876,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="571" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="571" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A571" s="1">
         <v>46161</v>
       </c>
@@ -11897,7 +11896,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="572" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="572" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A572" s="1">
         <v>46161</v>
       </c>
@@ -11917,7 +11916,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="573" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="573" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A573" s="1">
         <v>46161</v>
       </c>
@@ -11937,7 +11936,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="574" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="574" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A574" s="1">
         <v>46161</v>
       </c>
@@ -11957,7 +11956,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="575" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="575" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A575" s="1">
         <v>46161</v>
       </c>
@@ -11977,7 +11976,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="576" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="576" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A576" s="1">
         <v>46161</v>
       </c>
@@ -11997,7 +11996,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="577" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="577" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A577" s="1">
         <v>46161</v>
       </c>
@@ -12017,7 +12016,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="578" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="578" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A578" s="1">
         <v>46162</v>
       </c>
@@ -12037,7 +12036,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="579" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="579" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A579" s="1">
         <v>46162</v>
       </c>
@@ -12057,7 +12056,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="580" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="580" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A580" s="1">
         <v>46162</v>
       </c>
@@ -12077,7 +12076,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="581" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="581" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A581" s="1">
         <v>46162</v>
       </c>
@@ -12097,7 +12096,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="582" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="582" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A582" s="1">
         <v>46162</v>
       </c>
@@ -12117,7 +12116,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="583" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="583" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A583" s="1">
         <v>46162</v>
       </c>
@@ -12137,7 +12136,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="584" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="584" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A584" s="1">
         <v>46162</v>
       </c>
@@ -12157,7 +12156,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="585" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="585" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A585" s="1">
         <v>46162</v>
       </c>
@@ -12177,7 +12176,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="586" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="586" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A586" s="1">
         <v>46162</v>
       </c>
@@ -12197,7 +12196,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="587" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="587" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A587" s="1">
         <v>46162</v>
       </c>
@@ -12217,7 +12216,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="588" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="588" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A588" s="1">
         <v>46162</v>
       </c>
@@ -12237,7 +12236,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="589" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="589" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A589" s="1">
         <v>46162</v>
       </c>
@@ -12257,7 +12256,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="590" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="590" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A590" s="1">
         <v>46162</v>
       </c>
@@ -12277,7 +12276,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="591" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="591" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A591" s="1">
         <v>46162</v>
       </c>
@@ -12297,7 +12296,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="592" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="592" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A592" s="1">
         <v>46162</v>
       </c>
@@ -12317,7 +12316,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="593" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="593" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A593" s="1">
         <v>46162</v>
       </c>
@@ -12337,7 +12336,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="594" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="594" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A594" s="1">
         <v>46163</v>
       </c>
@@ -12357,7 +12356,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="595" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="595" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A595" s="1">
         <v>46163</v>
       </c>
@@ -12377,7 +12376,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="596" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="596" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A596" s="1">
         <v>46163</v>
       </c>
@@ -12397,7 +12396,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="597" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="597" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A597" s="1">
         <v>46163</v>
       </c>
@@ -12417,7 +12416,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="598" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="598" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A598" s="1">
         <v>46163</v>
       </c>
@@ -12437,7 +12436,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="599" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="599" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A599" s="1">
         <v>46163</v>
       </c>
@@ -12457,7 +12456,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="600" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="600" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A600" s="1">
         <v>46163</v>
       </c>
@@ -12477,7 +12476,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="601" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="601" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A601" s="1">
         <v>46163</v>
       </c>
@@ -12497,7 +12496,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="602" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="602" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A602" s="1">
         <v>46163</v>
       </c>
@@ -12517,7 +12516,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="603" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="603" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A603" s="1">
         <v>46163</v>
       </c>
@@ -12537,7 +12536,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="604" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="604" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A604" s="1">
         <v>46163</v>
       </c>
@@ -12557,7 +12556,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="605" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="605" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A605" s="1">
         <v>46163</v>
       </c>
@@ -12577,7 +12576,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="606" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="606" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A606" s="1">
         <v>46163</v>
       </c>
@@ -12597,7 +12596,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="607" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="607" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A607" s="1">
         <v>46163</v>
       </c>
@@ -12617,7 +12616,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="608" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="608" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A608" s="1">
         <v>46163</v>
       </c>
@@ -12637,7 +12636,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="609" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="609" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A609" s="1">
         <v>46163</v>
       </c>
@@ -12657,7 +12656,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="610" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="610" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A610" s="1">
         <v>46164</v>
       </c>
@@ -12677,7 +12676,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="611" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="611" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A611" s="1">
         <v>46164</v>
       </c>
@@ -12697,7 +12696,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="612" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="612" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A612" s="1">
         <v>46164</v>
       </c>
@@ -12717,7 +12716,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="613" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="613" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A613" s="1">
         <v>46164</v>
       </c>
@@ -12737,7 +12736,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="614" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="614" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A614" s="1">
         <v>46164</v>
       </c>
@@ -12757,7 +12756,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="615" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="615" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A615" s="1">
         <v>46164</v>
       </c>
@@ -12777,7 +12776,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="616" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="616" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A616" s="1">
         <v>46164</v>
       </c>
@@ -12797,7 +12796,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="617" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="617" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A617" s="1">
         <v>46164</v>
       </c>
@@ -12817,7 +12816,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="618" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="618" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A618" s="1">
         <v>46164</v>
       </c>
@@ -12837,7 +12836,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="619" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="619" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A619" s="1">
         <v>46164</v>
       </c>
@@ -12857,7 +12856,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="620" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="620" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A620" s="1">
         <v>46164</v>
       </c>
@@ -12877,7 +12876,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="621" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="621" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A621" s="1">
         <v>46164</v>
       </c>
@@ -12897,7 +12896,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="622" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="622" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A622" s="1">
         <v>46164</v>
       </c>
@@ -12917,7 +12916,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="623" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="623" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A623" s="1">
         <v>46164</v>
       </c>
@@ -12937,7 +12936,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="624" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="624" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A624" s="1">
         <v>46164</v>
       </c>
@@ -12957,7 +12956,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="625" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="625" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A625" s="1">
         <v>46165</v>
       </c>
@@ -12977,7 +12976,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="626" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="626" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A626" s="1">
         <v>46165</v>
       </c>
@@ -12997,7 +12996,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="627" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="627" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A627" s="1">
         <v>46165</v>
       </c>
@@ -13017,7 +13016,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="628" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="628" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A628" s="1">
         <v>46165</v>
       </c>
@@ -13037,7 +13036,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="629" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="629" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A629" s="1">
         <v>46165</v>
       </c>
@@ -13057,7 +13056,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="630" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="630" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A630" s="1">
         <v>46165</v>
       </c>
@@ -13077,7 +13076,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="631" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="631" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A631" s="1">
         <v>46165</v>
       </c>
@@ -13097,7 +13096,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="632" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="632" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A632" s="1">
         <v>46165</v>
       </c>
@@ -13117,7 +13116,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="633" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="633" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A633" s="1">
         <v>46165</v>
       </c>
@@ -13137,7 +13136,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="634" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="634" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A634" s="1">
         <v>46165</v>
       </c>
@@ -13157,7 +13156,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="635" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="635" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A635" s="1">
         <v>46165</v>
       </c>
@@ -13177,7 +13176,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="636" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="636" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A636" s="1">
         <v>46165</v>
       </c>
@@ -13197,7 +13196,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="637" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="637" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A637" s="1">
         <v>46165</v>
       </c>
@@ -13217,7 +13216,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="638" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="638" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A638" s="1">
         <v>46165</v>
       </c>
@@ -13237,7 +13236,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="639" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="639" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A639" s="1">
         <v>46165</v>
       </c>
@@ -13257,7 +13256,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="640" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="640" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A640" s="1">
         <v>46165</v>
       </c>
@@ -13277,7 +13276,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="641" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="641" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A641" s="1">
         <v>46166</v>
       </c>
@@ -13297,7 +13296,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="642" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="642" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A642" s="1">
         <v>46166</v>
       </c>
@@ -13317,7 +13316,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="643" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="643" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A643" s="1">
         <v>46166</v>
       </c>
@@ -13337,7 +13336,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="644" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="644" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A644" s="1">
         <v>46166</v>
       </c>
@@ -13357,7 +13356,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="645" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="645" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A645" s="1">
         <v>46166</v>
       </c>
@@ -13377,7 +13376,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="646" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="646" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A646" s="1">
         <v>46166</v>
       </c>
@@ -13397,7 +13396,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="647" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="647" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A647" s="1">
         <v>46166</v>
       </c>
@@ -13417,7 +13416,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="648" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="648" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A648" s="1">
         <v>46166</v>
       </c>
@@ -13437,7 +13436,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="649" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="649" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A649" s="1">
         <v>46166</v>
       </c>
@@ -13457,7 +13456,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="650" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="650" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A650" s="1">
         <v>46166</v>
       </c>
@@ -13477,7 +13476,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="651" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="651" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A651" s="1">
         <v>46166</v>
       </c>
@@ -13497,7 +13496,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="652" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="652" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A652" s="1">
         <v>46166</v>
       </c>
@@ -13517,7 +13516,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="653" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="653" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A653" s="1">
         <v>46166</v>
       </c>
@@ -13537,7 +13536,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="654" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="654" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A654" s="1">
         <v>46166</v>
       </c>
@@ -13557,7 +13556,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="655" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="655" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A655" s="1">
         <v>46166</v>
       </c>
@@ -13577,7 +13576,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="656" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="656" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A656" s="1">
         <v>46166</v>
       </c>
@@ -13597,7 +13596,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="657" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="657" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A657" s="1">
         <v>46167</v>
       </c>
@@ -13617,7 +13616,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="658" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="658" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A658" s="1">
         <v>46167</v>
       </c>
@@ -13637,7 +13636,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="659" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="659" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A659" s="1">
         <v>46167</v>
       </c>
@@ -13657,7 +13656,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="660" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="660" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A660" s="1">
         <v>46167</v>
       </c>
@@ -13677,7 +13676,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="661" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="661" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A661" s="1">
         <v>46167</v>
       </c>
@@ -13697,7 +13696,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="662" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="662" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A662" s="1">
         <v>46167</v>
       </c>
@@ -13717,7 +13716,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="663" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="663" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A663" s="1">
         <v>46167</v>
       </c>
@@ -13737,7 +13736,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="664" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="664" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A664" s="1">
         <v>46167</v>
       </c>
@@ -13757,7 +13756,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="665" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="665" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A665" s="1">
         <v>46167</v>
       </c>
@@ -13777,7 +13776,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="666" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="666" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A666" s="1">
         <v>46167</v>
       </c>
@@ -13797,7 +13796,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="667" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="667" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A667" s="1">
         <v>46167</v>
       </c>
@@ -13817,7 +13816,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="668" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="668" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A668" s="1">
         <v>46167</v>
       </c>
@@ -13837,7 +13836,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="669" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="669" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A669" s="1">
         <v>46167</v>
       </c>
@@ -13857,7 +13856,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="670" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="670" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A670" s="1">
         <v>46167</v>
       </c>
@@ -13877,7 +13876,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="671" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="671" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A671" s="1">
         <v>46167</v>
       </c>
@@ -13897,7 +13896,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="672" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="672" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A672" s="1">
         <v>46167</v>
       </c>
@@ -13917,7 +13916,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="673" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="673" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A673" s="1">
         <v>46168</v>
       </c>
@@ -13937,7 +13936,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="674" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="674" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A674" s="1">
         <v>46168</v>
       </c>
@@ -13957,7 +13956,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="675" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="675" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A675" s="1">
         <v>46168</v>
       </c>
@@ -13977,7 +13976,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="676" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="676" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A676" s="1">
         <v>46168</v>
       </c>
@@ -13997,7 +13996,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="677" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="677" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A677" s="1">
         <v>46168</v>
       </c>
@@ -14017,7 +14016,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="678" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="678" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A678" s="1">
         <v>46168</v>
       </c>
@@ -14037,7 +14036,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="679" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="679" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A679" s="1">
         <v>46168</v>
       </c>
@@ -14057,7 +14056,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="680" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="680" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A680" s="1">
         <v>46168</v>
       </c>
@@ -14077,7 +14076,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="681" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="681" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A681" s="1">
         <v>46168</v>
       </c>
@@ -14097,7 +14096,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="682" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="682" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A682" s="1">
         <v>46168</v>
       </c>
@@ -14117,7 +14116,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="683" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="683" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A683" s="1">
         <v>46168</v>
       </c>
@@ -14137,7 +14136,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="684" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="684" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A684" s="1">
         <v>46168</v>
       </c>
@@ -14157,7 +14156,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="685" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="685" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A685" s="1">
         <v>46168</v>
       </c>
@@ -14177,7 +14176,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="686" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="686" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A686" s="1">
         <v>46168</v>
       </c>
@@ -14197,7 +14196,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="687" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="687" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A687" s="1">
         <v>46168</v>
       </c>
@@ -14217,7 +14216,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="688" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="688" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A688" s="1">
         <v>46168</v>
       </c>
@@ -14237,7 +14236,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="689" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="689" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A689" s="1">
         <v>46168</v>
       </c>
@@ -14257,7 +14256,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="690" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="690" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A690" s="1">
         <v>46168</v>
       </c>
@@ -14277,7 +14276,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="691" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="691" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A691" s="1">
         <v>46169</v>
       </c>
@@ -14297,7 +14296,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="692" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="692" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A692" s="1">
         <v>46169</v>
       </c>
@@ -14317,7 +14316,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="693" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="693" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A693" s="1">
         <v>46169</v>
       </c>
@@ -14337,7 +14336,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="694" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="694" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A694" s="1">
         <v>46169</v>
       </c>
@@ -14357,7 +14356,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="695" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="695" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A695" s="1">
         <v>46169</v>
       </c>
@@ -14377,7 +14376,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="696" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="696" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A696" s="1">
         <v>46169</v>
       </c>
@@ -14397,7 +14396,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="697" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="697" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A697" s="1">
         <v>46169</v>
       </c>
@@ -14417,7 +14416,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="698" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="698" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A698" s="1">
         <v>46169</v>
       </c>
@@ -14437,7 +14436,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="699" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="699" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A699" s="1">
         <v>46169</v>
       </c>
@@ -14457,7 +14456,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="700" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="700" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A700" s="1">
         <v>46169</v>
       </c>
@@ -14477,7 +14476,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="701" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="701" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A701" s="1">
         <v>46169</v>
       </c>
@@ -14497,7 +14496,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="702" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="702" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A702" s="1">
         <v>46169</v>
       </c>
@@ -14517,7 +14516,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="703" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="703" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A703" s="1">
         <v>46169</v>
       </c>
@@ -14537,7 +14536,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="704" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="704" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A704" s="1">
         <v>46169</v>
       </c>
@@ -14557,7 +14556,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="705" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="705" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A705" s="1">
         <v>46169</v>
       </c>
@@ -14577,7 +14576,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="706" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="706" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A706" s="1">
         <v>46169</v>
       </c>
@@ -14597,7 +14596,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="707" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="707" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A707" s="1">
         <v>46169</v>
       </c>
@@ -14617,7 +14616,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="708" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="708" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A708" s="1">
         <v>46169</v>
       </c>
@@ -14637,7 +14636,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="709" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="709" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A709" s="1">
         <v>46170</v>
       </c>
@@ -14657,7 +14656,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="710" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="710" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A710" s="1">
         <v>46170</v>
       </c>
@@ -14677,7 +14676,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="711" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="711" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A711" s="1">
         <v>46170</v>
       </c>
@@ -14697,7 +14696,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="712" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="712" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A712" s="1">
         <v>46170</v>
       </c>
@@ -14717,7 +14716,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="713" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="713" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A713" s="1">
         <v>46170</v>
       </c>
@@ -14737,7 +14736,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="714" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="714" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A714" s="1">
         <v>46170</v>
       </c>
@@ -14757,7 +14756,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="715" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="715" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A715" s="1">
         <v>46170</v>
       </c>
@@ -14777,7 +14776,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="716" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="716" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A716" s="1">
         <v>46170</v>
       </c>
@@ -14797,7 +14796,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="717" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="717" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A717" s="1">
         <v>46170</v>
       </c>
@@ -14817,7 +14816,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="718" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="718" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A718" s="1">
         <v>46170</v>
       </c>
@@ -14837,7 +14836,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="719" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="719" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A719" s="1">
         <v>46170</v>
       </c>
@@ -14857,7 +14856,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="720" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="720" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A720" s="1">
         <v>46170</v>
       </c>
@@ -14877,7 +14876,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="721" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="721" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A721" s="1">
         <v>46170</v>
       </c>
@@ -14897,7 +14896,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="722" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="722" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A722" s="1">
         <v>46170</v>
       </c>
@@ -14917,7 +14916,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="723" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="723" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A723" s="1">
         <v>46170</v>
       </c>
@@ -14937,7 +14936,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="724" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="724" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A724" s="1">
         <v>46170</v>
       </c>
@@ -14957,7 +14956,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="725" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="725" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A725" s="1">
         <v>46170</v>
       </c>
@@ -14977,7 +14976,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="726" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="726" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A726" s="1">
         <v>46171</v>
       </c>
@@ -14997,7 +14996,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="727" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="727" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A727" s="1">
         <v>46171</v>
       </c>
@@ -15017,7 +15016,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="728" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="728" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A728" s="1">
         <v>46171</v>
       </c>
@@ -15037,7 +15036,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="729" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="729" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A729" s="1">
         <v>46171</v>
       </c>
@@ -15057,7 +15056,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="730" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="730" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A730" s="1">
         <v>46171</v>
       </c>
@@ -15077,7 +15076,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="731" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="731" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A731" s="1">
         <v>46171</v>
       </c>
@@ -15097,7 +15096,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="732" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="732" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A732" s="1">
         <v>46171</v>
       </c>
@@ -15117,7 +15116,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="733" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="733" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A733" s="1">
         <v>46171</v>
       </c>
@@ -15137,7 +15136,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="734" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="734" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A734" s="1">
         <v>46171</v>
       </c>
@@ -15157,7 +15156,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="735" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="735" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A735" s="1">
         <v>46171</v>
       </c>
@@ -15177,7 +15176,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="736" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="736" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A736" s="1">
         <v>46171</v>
       </c>
@@ -15197,7 +15196,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="737" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="737" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A737" s="1">
         <v>46171</v>
       </c>
@@ -15217,7 +15216,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="738" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="738" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A738" s="1">
         <v>46171</v>
       </c>
@@ -15237,7 +15236,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="739" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="739" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A739" s="1">
         <v>46171</v>
       </c>
@@ -15257,7 +15256,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="740" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="740" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A740" s="1">
         <v>46171</v>
       </c>
@@ -15277,7 +15276,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="741" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="741" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A741" s="1">
         <v>46171</v>
       </c>
@@ -15297,7 +15296,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="742" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="742" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A742" s="1">
         <v>46171</v>
       </c>
@@ -15317,7 +15316,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="743" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="743" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A743" s="1">
         <v>46171</v>
       </c>
@@ -15337,7 +15336,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="744" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="744" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A744" s="1">
         <v>46172</v>
       </c>
@@ -15357,7 +15356,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="745" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="745" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A745" s="1">
         <v>46172</v>
       </c>
@@ -15377,7 +15376,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="746" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="746" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A746" s="1">
         <v>46172</v>
       </c>
@@ -15397,7 +15396,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="747" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="747" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A747" s="1">
         <v>46172</v>
       </c>
@@ -15417,7 +15416,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="748" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="748" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A748" s="1">
         <v>46172</v>
       </c>
@@ -15437,7 +15436,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="749" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="749" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A749" s="1">
         <v>46172</v>
       </c>
@@ -15457,7 +15456,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="750" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="750" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A750" s="1">
         <v>46172</v>
       </c>
@@ -15477,7 +15476,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="751" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="751" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A751" s="1">
         <v>46172</v>
       </c>
@@ -15497,7 +15496,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="752" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="752" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A752" s="1">
         <v>46172</v>
       </c>
@@ -15517,7 +15516,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="753" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="753" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A753" s="1">
         <v>46172</v>
       </c>
@@ -15537,7 +15536,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="754" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="754" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A754" s="1">
         <v>46172</v>
       </c>
@@ -15557,7 +15556,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="755" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="755" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A755" s="1">
         <v>46172</v>
       </c>
@@ -15577,7 +15576,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="756" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="756" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A756" s="1">
         <v>46172</v>
       </c>
@@ -15597,7 +15596,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="757" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="757" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A757" s="1">
         <v>46172</v>
       </c>
@@ -15617,7 +15616,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="758" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="758" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A758" s="1">
         <v>46172</v>
       </c>
@@ -15637,7 +15636,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="759" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="759" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A759" s="1">
         <v>46172</v>
       </c>
@@ -15657,7 +15656,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="760" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="760" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A760" s="1">
         <v>46172</v>
       </c>
@@ -15677,7 +15676,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="761" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="761" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A761" s="1">
         <v>46172</v>
       </c>
@@ -15697,7 +15696,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="762" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="762" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A762" s="1">
         <v>46173</v>
       </c>
@@ -15717,7 +15716,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="763" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="763" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A763" s="1">
         <v>46173</v>
       </c>
@@ -15737,7 +15736,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="764" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="764" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A764" s="1">
         <v>46173</v>
       </c>
@@ -15757,7 +15756,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="765" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="765" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A765" s="1">
         <v>46173</v>
       </c>
@@ -15777,7 +15776,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="766" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="766" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A766" s="1">
         <v>46173</v>
       </c>
@@ -15797,7 +15796,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="767" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="767" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A767" s="1">
         <v>46173</v>
       </c>
@@ -15817,7 +15816,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="768" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="768" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A768" s="1">
         <v>46173</v>
       </c>
@@ -15837,7 +15836,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="769" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="769" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A769" s="1">
         <v>46173</v>
       </c>
@@ -15857,7 +15856,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="770" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="770" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A770" s="1">
         <v>46173</v>
       </c>
@@ -15877,7 +15876,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="771" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="771" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A771" s="1">
         <v>46173</v>
       </c>
@@ -15897,7 +15896,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="772" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="772" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A772" s="1">
         <v>46173</v>
       </c>
@@ -15917,7 +15916,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="773" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="773" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A773" s="1">
         <v>46173</v>
       </c>
@@ -15937,7 +15936,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="774" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="774" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A774" s="1">
         <v>46173</v>
       </c>
@@ -15957,7 +15956,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="775" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="775" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A775" s="1">
         <v>46173</v>
       </c>
@@ -15977,7 +15976,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="776" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="776" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A776" s="1">
         <v>46173</v>
       </c>
@@ -15997,7 +15996,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="777" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="777" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A777" s="1">
         <v>46173</v>
       </c>
@@ -19738,13 +19737,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F896" xr:uid="{22A7DA2E-DF85-4559-9E8B-F6EDBCD02D26}">
-    <filterColumn colId="0">
-      <filters>
-        <dateGroupItem year="2026" month="6" dateTimeGrouping="month"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:F963" xr:uid="{22A7DA2E-DF85-4559-9E8B-F6EDBCD02D26}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>